--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_24sep26_Thurs.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_24sep26_Thurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D4D194-1FF0-401A-A16E-8637CF812EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5E1FB5-A390-4B44-9FD5-9C72E9E41FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Sheet1 (2)" sheetId="9" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sheet1 (2)'!$A$1:$P$295</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$N$6</definedName>
   </definedNames>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3449" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3451" uniqueCount="315">
   <si>
     <t>Date</t>
   </si>
@@ -1142,7 +1142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1320,18 +1320,6 @@
     <xf numFmtId="22" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="22" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -1344,8 +1332,8 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1649,7 +1637,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P985"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1746,7 +1733,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B2, $C$2:$C$709, C2, $D$2:$D$709, D2, $E$2:$E$709, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$709, B2, $C$2:$C$709, C2, $D$2:$D$709, D2, $E$2:$E$709, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -1787,7 +1774,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B3, $C$2:$C$709, C3, $D$2:$D$709, D3, $E$2:$E$709, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -1831,7 +1818,7 @@
         <v>3156</v>
       </c>
       <c r="N4" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B4, $C$2:$C$709, C4, $D$2:$D$709, D4, $E$2:$E$709, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -1879,7 +1866,7 @@
         <v>34175</v>
       </c>
       <c r="N5" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B5, $C$2:$C$709, C5, $D$2:$D$709, D5, $E$2:$E$709, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -1920,7 +1907,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B6, $C$2:$C$709, C6, $D$2:$D$709, D6, $E$2:$E$709, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="10"/>
@@ -1961,7 +1948,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B7, $C$2:$C$709, C7, $D$2:$D$709, D7, $E$2:$E$709, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="10"/>
@@ -2000,7 +1987,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B8, $C$2:$C$709, C8, $D$2:$D$709, D8, $E$2:$E$709, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="25"/>
@@ -2048,7 +2035,7 @@
         <v>350</v>
       </c>
       <c r="N9" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B9, $C$2:$C$709, C9, $D$2:$D$709, D9, $E$2:$E$709, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="10"/>
@@ -2087,7 +2074,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B10, $C$2:$C$709, C10, $D$2:$D$709, D10, $E$2:$E$709, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="19"/>
@@ -2135,7 +2122,7 @@
         <v>300</v>
       </c>
       <c r="N11" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B11, $C$2:$C$709, C11, $D$2:$D$709, D11, $E$2:$E$709, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O11" s="30"/>
@@ -2183,7 +2170,7 @@
         <v>200</v>
       </c>
       <c r="N12" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B12, $C$2:$C$709, C12, $D$2:$D$709, D12, $E$2:$E$709, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O12" s="30"/>
@@ -2222,7 +2209,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B13, $C$2:$C$709, C13, $D$2:$D$709, D13, $E$2:$E$709, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="10"/>
@@ -2263,7 +2250,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B14, $C$2:$C$709, C14, $D$2:$D$709, D14, $E$2:$E$709, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2309,7 +2296,7 @@
         <v>500</v>
       </c>
       <c r="N15" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B15, $C$2:$C$709, C15, $D$2:$D$709, D15, $E$2:$E$709, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15" s="10"/>
@@ -2350,7 +2337,7 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B16, $C$2:$C$709, C16, $D$2:$D$709, D16, $E$2:$E$709, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16" s="29"/>
@@ -2397,7 +2384,7 @@
         <v>700</v>
       </c>
       <c r="N17" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B17, $C$2:$C$709, C17, $D$2:$D$709, D17, $E$2:$E$709, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17" s="10"/>
@@ -2438,7 +2425,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B18, $C$2:$C$709, C18, $D$2:$D$709, D18, $E$2:$E$709, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18" s="10"/>
@@ -2486,7 +2473,7 @@
         <v>650</v>
       </c>
       <c r="N19" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B19, $C$2:$C$709, C19, $D$2:$D$709, D19, $E$2:$E$709, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2523,7 +2510,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B20, $C$2:$C$709, C20, $D$2:$D$709, D20, $E$2:$E$709, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2569,7 +2556,7 @@
         <v>516</v>
       </c>
       <c r="N21" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B21, $C$2:$C$709, C21, $D$2:$D$709, D21, $E$2:$E$709, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2615,7 +2602,7 @@
         <v>720</v>
       </c>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B22, $C$2:$C$709, C22, $D$2:$D$709, D22, $E$2:$E$709, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2661,7 +2648,7 @@
         <v>300</v>
       </c>
       <c r="N23" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B23, $C$2:$C$709, C23, $D$2:$D$709, D23, $E$2:$E$709, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P23" s="24"/>
@@ -2701,7 +2688,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B24, $C$2:$C$709, C24, $D$2:$D$709, D24, $E$2:$E$709, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24"/>
@@ -2742,7 +2729,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B25, $C$2:$C$709, C25, $D$2:$D$709, D25, $E$2:$E$709, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25"/>
@@ -2783,7 +2770,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B26, $C$2:$C$709, C26, $D$2:$D$709, D26, $E$2:$E$709, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2822,7 +2809,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B27, $C$2:$C$709, C27, $D$2:$D$709, D27, $E$2:$E$709, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2868,7 +2855,7 @@
         <v>650</v>
       </c>
       <c r="N28" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B28, $C$2:$C$709, C28, $D$2:$D$709, D28, $E$2:$E$709, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2915,7 +2902,7 @@
         <v>175</v>
       </c>
       <c r="N29" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B29, $C$2:$C$709, C29, $D$2:$D$709, D29, $E$2:$E$709, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29" s="10"/>
@@ -2963,7 +2950,7 @@
         <v>300</v>
       </c>
       <c r="N30" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B30, $C$2:$C$709, C30, $D$2:$D$709, D30, $E$2:$E$709, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3002,7 +2989,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B31, $C$2:$C$709, C31, $D$2:$D$709, D31, $E$2:$E$709, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31"/>
@@ -3041,7 +3028,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B32, $C$2:$C$709, C32, $D$2:$D$709, D32, $E$2:$E$709, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32"/>
@@ -3075,13 +3062,13 @@
         <v>8</v>
       </c>
       <c r="J33" s="22" t="s">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="K33" s="17"/>
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B33, $C$2:$C$709, C33, $D$2:$D$709, D33, $E$2:$E$709, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33"/>
@@ -3122,7 +3109,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B34, $C$2:$C$709, C34, $D$2:$D$709, D34, $E$2:$E$709, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34"/>
@@ -3161,7 +3148,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B35, $C$2:$C$709, C35, $D$2:$D$709, D35, $E$2:$E$709, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35"/>
@@ -3201,7 +3188,7 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B36, $C$2:$C$709, C36, $D$2:$D$709, D36, $E$2:$E$709, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36"/>
@@ -3240,7 +3227,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B37, $C$2:$C$709, C37, $D$2:$D$709, D37, $E$2:$E$709, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37"/>
@@ -3289,7 +3276,7 @@
         <v>225</v>
       </c>
       <c r="N38" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B38, $C$2:$C$709, C38, $D$2:$D$709, D38, $E$2:$E$709, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3335,7 +3322,7 @@
         <v>300</v>
       </c>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B39, $C$2:$C$709, C39, $D$2:$D$709, D39, $E$2:$E$709, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3374,7 +3361,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B40, $C$2:$C$709, C40, $D$2:$D$709, D40, $E$2:$E$709, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P40"/>
@@ -3421,7 +3408,7 @@
         <v>525</v>
       </c>
       <c r="N41" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B41, $C$2:$C$709, C41, $D$2:$D$709, D41, $E$2:$E$709, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3458,7 +3445,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B42, $C$2:$C$709, C42, $D$2:$D$709, D42, $E$2:$E$709, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42"/>
@@ -3499,7 +3486,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B43, $C$2:$C$709, C43, $D$2:$D$709, D43, $E$2:$E$709, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43"/>
@@ -3540,7 +3527,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B44, $C$2:$C$709, C44, $D$2:$D$709, D44, $E$2:$E$709, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44"/>
@@ -3589,7 +3576,7 @@
         <v>540</v>
       </c>
       <c r="N45" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B45, $C$2:$C$709, C45, $D$2:$D$709, D45, $E$2:$E$709, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -3628,7 +3615,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B46, $C$2:$C$709, C46, $D$2:$D$709, D46, $E$2:$E$709, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
@@ -3663,13 +3650,13 @@
         <v>8</v>
       </c>
       <c r="J47" s="36" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B47, $C$2:$C$709, C47, $D$2:$D$709, D47, $E$2:$E$709, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -3708,7 +3695,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B48, $C$2:$C$709, C48, $D$2:$D$709, D48, $E$2:$E$709, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48"/>
@@ -3756,7 +3743,7 @@
         <v>314</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B49, $C$2:$C$709, C49, $D$2:$D$709, D49, $E$2:$E$709, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3795,7 +3782,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B50, $C$2:$C$709, C50, $D$2:$D$709, D50, $E$2:$E$709, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50"/>
@@ -3833,7 +3820,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B51, $C$2:$C$709, C51, $D$2:$D$709, D51, $E$2:$E$709, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51"/>
@@ -3872,7 +3859,7 @@
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B52, $C$2:$C$709, C52, $D$2:$D$709, D52, $E$2:$E$709, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52"/>
@@ -3911,7 +3898,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B53, $C$2:$C$709, C53, $D$2:$D$709, D53, $E$2:$E$709, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53"/>
@@ -3952,7 +3939,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B54, $C$2:$C$709, C54, $D$2:$D$709, D54, $E$2:$E$709, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -3991,7 +3978,7 @@
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B55, $C$2:$C$709, C55, $D$2:$D$709, D55, $E$2:$E$709, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -4039,7 +4026,7 @@
         <v>240</v>
       </c>
       <c r="N56" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B56, $C$2:$C$709, C56, $D$2:$D$709, D56, $E$2:$E$709, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56" s="10"/>
@@ -4087,7 +4074,7 @@
         <v>300</v>
       </c>
       <c r="N57" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B57, $C$2:$C$709, C57, $D$2:$D$709, D57, $E$2:$E$709, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
@@ -4126,7 +4113,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B58, $C$2:$C$709, C58, $D$2:$D$709, D58, $E$2:$E$709, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
@@ -4160,12 +4147,12 @@
       <c r="I59" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="61"/>
+      <c r="J59" s="50"/>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B59, $C$2:$C$709, C59, $D$2:$D$709, D59, $E$2:$E$709, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4197,7 +4184,7 @@
       <c r="I60" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J60" s="69" t="s">
+      <c r="J60" s="17" t="s">
         <v>55</v>
       </c>
       <c r="K60" s="17" t="s">
@@ -4206,7 +4193,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B60, $C$2:$C$709, C60, $D$2:$D$709, D60, $E$2:$E$709, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4238,12 +4225,12 @@
       <c r="I61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J61" s="61"/>
+      <c r="J61" s="50"/>
       <c r="K61" s="17"/>
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B61, $C$2:$C$709, C61, $D$2:$D$709, D61, $E$2:$E$709, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4275,7 +4262,7 @@
       <c r="I62" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="63" t="s">
+      <c r="J62" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K62" s="18" t="s">
@@ -4289,7 +4276,7 @@
         <v>250</v>
       </c>
       <c r="N62" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B62, $C$2:$C$709, C62, $D$2:$D$709, D62, $E$2:$E$709, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62" s="10"/>
@@ -4323,12 +4310,12 @@
       <c r="I63" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J63" s="61"/>
+      <c r="J63" s="50"/>
       <c r="K63" s="17"/>
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B63, $C$2:$C$709, C63, $D$2:$D$709, D63, $E$2:$E$709, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4360,12 +4347,12 @@
       <c r="I64" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J64" s="61"/>
+      <c r="J64" s="50"/>
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B64, $C$2:$C$709, C64, $D$2:$D$709, D64, $E$2:$E$709, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4397,14 +4384,14 @@
       <c r="I65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J65" s="61" t="s">
+      <c r="J65" s="50" t="s">
         <v>41</v>
       </c>
       <c r="K65" s="17"/>
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B65, $C$2:$C$709, C65, $D$2:$D$709, D65, $E$2:$E$709, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65"/>
@@ -4438,14 +4425,14 @@
       <c r="I66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="61" t="s">
+      <c r="J66" s="50" t="s">
         <v>41</v>
       </c>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B66, $C$2:$C$709, C66, $D$2:$D$709, D66, $E$2:$E$709, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$709, B66, $C$2:$C$709, C66, $D$2:$D$709, D66, $E$2:$E$709, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66"/>
@@ -4479,12 +4466,12 @@
       <c r="I67" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J67" s="61"/>
+      <c r="J67" s="50"/>
       <c r="K67" s="17"/>
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B67, $C$2:$C$709, C67, $D$2:$D$709, D67, $E$2:$E$709, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67"/>
@@ -4518,12 +4505,12 @@
       <c r="I68" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J68" s="61"/>
+      <c r="J68" s="50"/>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B68, $C$2:$C$709, C68, $D$2:$D$709, D68, $E$2:$E$709, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68"/>
@@ -4557,7 +4544,7 @@
       <c r="I69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="63" t="s">
+      <c r="J69" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K69" s="18" t="s">
@@ -4571,7 +4558,7 @@
         <v>302</v>
       </c>
       <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B69, $C$2:$C$709, C69, $D$2:$D$709, D69, $E$2:$E$709, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4603,14 +4590,14 @@
       <c r="I70" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J70" s="61" t="s">
+      <c r="J70" s="50" t="s">
         <v>41</v>
       </c>
       <c r="K70" s="17"/>
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B70, $C$2:$C$709, C70, $D$2:$D$709, D70, $E$2:$E$709, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70"/>
@@ -4644,7 +4631,7 @@
       <c r="I71" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J71" s="63" t="s">
+      <c r="J71" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K71" s="18" t="s">
@@ -4658,7 +4645,7 @@
         <v>10680</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B71, $C$2:$C$709, C71, $D$2:$D$709, D71, $E$2:$E$709, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4690,14 +4677,14 @@
       <c r="I72" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J72" s="64" t="s">
+      <c r="J72" s="51" t="s">
         <v>41</v>
       </c>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B72, $C$2:$C$709, C72, $D$2:$D$709, D72, $E$2:$E$709, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72"/>
@@ -4731,7 +4718,7 @@
       <c r="I73" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J73" s="63" t="s">
+      <c r="J73" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K73" s="18" t="s">
@@ -4745,7 +4732,7 @@
         <v>10880</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B73, $C$2:$C$709, C73, $D$2:$D$709, D73, $E$2:$E$709, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4777,20 +4764,20 @@
       <c r="I74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J74" s="61" t="s">
+      <c r="J74" s="50" t="s">
         <v>41</v>
       </c>
       <c r="K74" s="17"/>
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B74, $C$2:$C$709, C74, $D$2:$D$709, D74, $E$2:$E$709, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74"/>
       <c r="P74"/>
     </row>
-    <row r="75" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="3">
         <v>46274.375</v>
       </c>
@@ -4832,7 +4819,7 @@
         <v>300</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B75, $C$2:$C$709, C75, $D$2:$D$709, D75, $E$2:$E$709, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O75" s="39" t="s">
@@ -4868,20 +4855,20 @@
       <c r="I76" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J76" s="61" t="s">
+      <c r="J76" s="50" t="s">
         <v>55</v>
       </c>
       <c r="K76" s="17"/>
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B76, $C$2:$C$709, C76, $D$2:$D$709, D76, $E$2:$E$709, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76"/>
       <c r="P76"/>
     </row>
-    <row r="77" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="3">
         <v>46268.375</v>
       </c>
@@ -4923,7 +4910,7 @@
         <v>1200</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B77, $C$2:$C$709, C77, $D$2:$D$709, D77, $E$2:$E$709, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4955,18 +4942,18 @@
       <c r="I78" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J78" s="61"/>
+      <c r="J78" s="50"/>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B78, $C$2:$C$709, C78, $D$2:$D$709, D78, $E$2:$E$709, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78"/>
       <c r="P78"/>
     </row>
-    <row r="79" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="3">
         <v>46281.376388888886</v>
       </c>
@@ -5008,8 +4995,11 @@
         <v>300</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B79, $C$2:$C$709, C79, $D$2:$D$709, D79, $E$2:$E$709, E79) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O79" s="39" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -5040,20 +5030,20 @@
       <c r="I80" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J80" s="61" t="s">
+      <c r="J80" s="50" t="s">
         <v>41</v>
       </c>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
       <c r="N80" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B80, $C$2:$C$709, C80, $D$2:$D$709, D80, $E$2:$E$709, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O80"/>
       <c r="P80"/>
     </row>
-    <row r="81" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="3">
         <v>46286.375694444447</v>
       </c>
@@ -5096,11 +5086,11 @@
         <v>300</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B81, $C$2:$C$709, C81, $D$2:$D$709, D81, $E$2:$E$709, E81) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="3">
         <v>46276.375</v>
       </c>
@@ -5142,11 +5132,14 @@
         <v>646</v>
       </c>
       <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B82, $C$2:$C$709, C82, $D$2:$D$709, D82, $E$2:$E$709, E82) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" s="24" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O82" s="39" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" s="24" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="3">
         <v>46287.375</v>
       </c>
@@ -5188,13 +5181,13 @@
         <v>300</v>
       </c>
       <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B83, $C$2:$C$709, C83, $D$2:$D$709, D83, $E$2:$E$709, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O83" s="10"/>
       <c r="P83" s="10"/>
     </row>
-    <row r="84" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="60">
         <v>46289.375694444447</v>
       </c>
@@ -5236,11 +5229,11 @@
         <v>300</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B84, $C$2:$C$709, C84, $D$2:$D$709, D84, $E$2:$E$709, E84) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="3">
         <v>46280.435416666667</v>
       </c>
@@ -5282,11 +5275,11 @@
         <v>18850</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B85, $C$2:$C$709, C85, $D$2:$D$709, D85, $E$2:$E$709, E85) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="8" t="s">
         <v>62</v>
       </c>
@@ -5316,11 +5309,11 @@
       </c>
       <c r="J86" s="35"/>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B86, $C$2:$C$709, C86, $D$2:$D$709, D86, $E$2:$E$709, E86) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="31">
         <v>46281.443055555559</v>
       </c>
@@ -5358,11 +5351,11 @@
         <v>5585</v>
       </c>
       <c r="M87" s="28">
-        <f>ABS((D87*E87)-L87)</f>
+        <f t="shared" ref="M87:M94" si="2">ABS((D87*E87)-L87)</f>
         <v>395</v>
       </c>
       <c r="N87" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B87, $C$2:$C$709, C87, $D$2:$D$709, D87, $E$2:$E$709, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O87" s="39" t="s">
@@ -5370,7 +5363,7 @@
       </c>
       <c r="P87" s="30"/>
     </row>
-    <row r="88" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="31">
         <v>46281.388888888891</v>
       </c>
@@ -5408,11 +5401,11 @@
         <v>5730</v>
       </c>
       <c r="M88" s="28">
-        <f>ABS((D88*E88)-L88)</f>
+        <f t="shared" si="2"/>
         <v>250</v>
       </c>
       <c r="N88" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B88, $C$2:$C$709, C88, $D$2:$D$709, D88, $E$2:$E$709, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O88" s="39" t="s">
@@ -5420,7 +5413,7 @@
       </c>
       <c r="P88" s="30"/>
     </row>
-    <row r="89" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="3">
         <v>46267.461111111108</v>
       </c>
@@ -5458,15 +5451,15 @@
         <v>32900</v>
       </c>
       <c r="M89" s="18">
-        <f>ABS((D89*E89)-L89)</f>
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B89, $C$2:$C$709, C89, $D$2:$D$709, D89, $E$2:$E$709, E89) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="41">
         <v>46273.375</v>
       </c>
@@ -5504,18 +5497,18 @@
         <v>19730.5</v>
       </c>
       <c r="M90" s="28">
-        <f>ABS((D90*E90)-L90)</f>
+        <f t="shared" si="2"/>
         <v>504.5</v>
       </c>
       <c r="N90" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B90, $C$2:$C$709, C90, $D$2:$D$709, D90, $E$2:$E$709, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O90" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="91" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="31">
         <v>46274.375</v>
       </c>
@@ -5553,18 +5546,18 @@
         <v>19690</v>
       </c>
       <c r="M91" s="28">
-        <f>ABS((D91*E91)-L91)</f>
+        <f t="shared" si="2"/>
         <v>545</v>
       </c>
       <c r="N91" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B91, $C$2:$C$709, C91, $D$2:$D$709, D91, $E$2:$E$709, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O91" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="11">
         <v>46273.375</v>
       </c>
@@ -5602,18 +5595,18 @@
         <v>9170</v>
       </c>
       <c r="M92" s="28">
-        <f>ABS((D92*E92)-L92)</f>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
       <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B92, $C$2:$C$709, C92, $D$2:$D$709, D92, $E$2:$E$709, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O92" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="3">
         <v>46267.375</v>
       </c>
@@ -5651,18 +5644,18 @@
         <v>8220</v>
       </c>
       <c r="M93" s="18">
-        <f>ABS((D93*E93)-L93)</f>
+        <f t="shared" si="2"/>
         <v>360</v>
       </c>
       <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B93, $C$2:$C$709, C93, $D$2:$D$709, D93, $E$2:$E$709, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O93" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="3">
         <v>46286.468055555553</v>
       </c>
@@ -5700,12 +5693,15 @@
         <v>6367.2</v>
       </c>
       <c r="M94" s="18">
-        <f>ABS((D94*E94)-L94)</f>
+        <f t="shared" si="2"/>
         <v>300.80000000000018</v>
       </c>
       <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B94, $C$2:$C$709, C94, $D$2:$D$709, D94, $E$2:$E$709, E94) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O94" s="39" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
@@ -5736,20 +5732,20 @@
       <c r="I95" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J95" s="61" t="s">
+      <c r="J95" s="50" t="s">
         <v>41</v>
       </c>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="17"/>
       <c r="N95" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B95, $C$2:$C$709, C95, $D$2:$D$709, D95, $E$2:$E$709, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O95"/>
       <c r="P95"/>
     </row>
-    <row r="96" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="3">
         <v>46267.375</v>
       </c>
@@ -5787,15 +5783,15 @@
         <v>16755</v>
       </c>
       <c r="M96" s="18">
-        <f>ABS((D96*E96)-L96)</f>
+        <f t="shared" ref="M96:M104" si="3">ABS((D96*E96)-L96)</f>
         <v>295</v>
       </c>
       <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B96, $C$2:$C$709, C96, $D$2:$D$709, D96, $E$2:$E$709, E96) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="31">
         <v>46267.375</v>
       </c>
@@ -5833,15 +5829,15 @@
         <v>5755</v>
       </c>
       <c r="M97" s="28">
-        <f>ABS((D97*E97)-L97)</f>
+        <f t="shared" si="3"/>
         <v>275</v>
       </c>
       <c r="N97" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B97, $C$2:$C$709, C97, $D$2:$D$709, D97, $E$2:$E$709, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="31">
         <v>46267.375</v>
       </c>
@@ -5879,15 +5875,15 @@
         <v>5805</v>
       </c>
       <c r="M98" s="28">
-        <f>ABS((D98*E98)-L98)</f>
+        <f t="shared" si="3"/>
         <v>225</v>
       </c>
       <c r="N98" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B98, $C$2:$C$709, C98, $D$2:$D$709, D98, $E$2:$E$709, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="3">
         <v>46275.375</v>
       </c>
@@ -5925,15 +5921,15 @@
         <v>10400</v>
       </c>
       <c r="M99" s="18">
-        <f>ABS((D99*E99)-L99)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B99, $C$2:$C$709, C99, $D$2:$D$709, D99, $E$2:$E$709, E99) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="11">
         <v>46253.375</v>
       </c>
@@ -5972,15 +5968,15 @@
         <v>3160</v>
       </c>
       <c r="M100" s="18">
-        <f>ABS((D100*E100)-L100)</f>
+        <f t="shared" si="3"/>
         <v>235</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B100, $C$2:$C$709, C100, $D$2:$D$709, D100, $E$2:$E$709, E100) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3">
         <v>46275.375</v>
       </c>
@@ -6018,15 +6014,15 @@
         <v>3300</v>
       </c>
       <c r="M101" s="18">
-        <f>ABS((D101*E101)-L101)</f>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B101, $C$2:$C$709, C101, $D$2:$D$709, D101, $E$2:$E$709, E101) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" s="30" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" s="30" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3">
         <v>46288.429861111108</v>
       </c>
@@ -6064,17 +6060,17 @@
         <v>14130</v>
       </c>
       <c r="M102" s="18">
-        <f>ABS((D102*E102)-L102)</f>
+        <f t="shared" si="3"/>
         <v>714</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B102, $C$2:$C$709, C102, $D$2:$D$709, D102, $E$2:$E$709, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="10"/>
       <c r="P102" s="10"/>
     </row>
-    <row r="103" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="11">
         <v>46273.375</v>
       </c>
@@ -6112,15 +6108,15 @@
         <v>9170</v>
       </c>
       <c r="M103" s="28">
-        <f>ABS((D103*E103)-L103)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B103, $C$2:$C$709, C103, $D$2:$D$709, D103, $E$2:$E$709, E103) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -6158,16 +6154,16 @@
         <v>20010</v>
       </c>
       <c r="M104" s="18">
-        <f>ABS((D104*E104)-L104)</f>
+        <f t="shared" si="3"/>
         <v>450</v>
       </c>
       <c r="N104" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B104, $C$2:$C$709, C104, $D$2:$D$709, D104, $E$2:$E$709, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P104"/>
     </row>
-    <row r="105" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="8" t="s">
         <v>62</v>
       </c>
@@ -6199,11 +6195,11 @@
         <v>118</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B105, $C$2:$C$709, C105, $D$2:$D$709, D105, $E$2:$E$709, E105) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3">
         <v>46267.38958333333</v>
       </c>
@@ -6241,15 +6237,15 @@
         <v>33200</v>
       </c>
       <c r="M106" s="18">
-        <f>ABS((D106*E106)-L106)</f>
+        <f t="shared" ref="M106:M112" si="4">ABS((D106*E106)-L106)</f>
         <v>1200</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B106, $C$2:$C$709, C106, $D$2:$D$709, D106, $E$2:$E$709, E106) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3">
         <v>46280.375694444447</v>
       </c>
@@ -6287,11 +6283,11 @@
         <v>10249</v>
       </c>
       <c r="M107" s="18">
-        <f>ABS((D107*E107)-L107)</f>
+        <f t="shared" si="4"/>
         <v>4451</v>
       </c>
       <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B107, $C$2:$C$709, C107, $D$2:$D$709, D107, $E$2:$E$709, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="39" t="s">
@@ -6299,7 +6295,7 @@
       </c>
       <c r="P107" s="10"/>
     </row>
-    <row r="108" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3">
         <v>46260.375694444447</v>
       </c>
@@ -6337,17 +6333,17 @@
         <v>20260</v>
       </c>
       <c r="M108" s="18">
-        <f>ABS((D108*E108)-L108)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N108" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B108, $C$2:$C$709, C108, $D$2:$D$709, D108, $E$2:$E$709, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O108"/>
       <c r="P108" s="30"/>
     </row>
-    <row r="109" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="3">
         <v>46280.435416666667</v>
       </c>
@@ -6385,15 +6381,15 @@
         <v>39300</v>
       </c>
       <c r="M109" s="18">
-        <f>ABS((D109*E109)-L109)</f>
+        <f t="shared" si="4"/>
         <v>18350</v>
       </c>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B109, $C$2:$C$709, C109, $D$2:$D$709, D109, $E$2:$E$709, E109) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="31">
         <v>46267.425694444442</v>
       </c>
@@ -6431,19 +6427,19 @@
         <v>4120</v>
       </c>
       <c r="M110" s="28">
-        <f>ABS((D110*E110)-L110)</f>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="N110" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B110, $C$2:$C$709, C110, $D$2:$D$709, D110, $E$2:$E$709, E110) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O110" s="29" t="s">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O110" s="40" t="s">
         <v>242</v>
       </c>
       <c r="P110" s="30"/>
     </row>
-    <row r="111" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="31">
         <v>46280.593055555553</v>
       </c>
@@ -6481,19 +6477,19 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M111" s="28">
-        <f>ABS((D111*E111)-L111)</f>
+        <f t="shared" si="4"/>
         <v>188.60000000000014</v>
       </c>
       <c r="N111" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B111, $C$2:$C$709, C111, $D$2:$D$709, D111, $E$2:$E$709, E111) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O111" s="29" t="s">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O111" s="40" t="s">
         <v>242</v>
       </c>
       <c r="P111" s="30"/>
     </row>
-    <row r="112" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3">
         <v>46262.375</v>
       </c>
@@ -6531,15 +6527,15 @@
         <v>8420</v>
       </c>
       <c r="M112" s="18">
-        <f>ABS((D112*E112)-L112)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B112, $C$2:$C$709, C112, $D$2:$D$709, D112, $E$2:$E$709, E112) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6569,11 +6565,11 @@
       </c>
       <c r="J113" s="35"/>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B113, $C$2:$C$709, C113, $D$2:$D$709, D113, $E$2:$E$709, E113) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3">
         <v>46335.442361111112</v>
       </c>
@@ -6611,15 +6607,15 @@
         <v>14100</v>
       </c>
       <c r="M114" s="18">
-        <f>ABS((D114*E114)-L114)</f>
+        <f t="shared" ref="M114:M124" si="5">ABS((D114*E114)-L114)</f>
         <v>500</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B114, $C$2:$C$709, C114, $D$2:$D$709, D114, $E$2:$E$709, E114) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3">
         <v>46267.375</v>
       </c>
@@ -6657,16 +6653,16 @@
         <v>9270</v>
       </c>
       <c r="M115" s="18">
-        <f>ABS((D115*E115)-L115)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B115, $C$2:$C$709, C115, $D$2:$D$709, D115, $E$2:$E$709, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P115" s="19"/>
     </row>
-    <row r="116" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -6704,15 +6700,15 @@
         <v>5940</v>
       </c>
       <c r="M116" s="18">
-        <f>ABS((D116*E116)-L116)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B116, $C$2:$C$709, C116, $D$2:$D$709, D116, $E$2:$E$709, E116) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -6750,18 +6746,18 @@
         <v>15075</v>
       </c>
       <c r="M117" s="18">
-        <f>ABS((D117*E117)-L117)</f>
+        <f t="shared" si="5"/>
         <v>645</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B117, $C$2:$C$709, C117, $D$2:$D$709, D117, $E$2:$E$709, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="3">
         <v>46266.642361111109</v>
       </c>
@@ -6799,15 +6795,15 @@
         <v>33950</v>
       </c>
       <c r="M118" s="18">
-        <f>ABS((D118*E118)-L118)</f>
+        <f t="shared" si="5"/>
         <v>850</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B118, $C$2:$C$709, C118, $D$2:$D$709, D118, $E$2:$E$709, E118) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="60">
         <v>46289.390462962961</v>
       </c>
@@ -6845,15 +6841,15 @@
         <v>9886</v>
       </c>
       <c r="M119" s="18">
-        <f>ABS((D119*E119)-L119)</f>
+        <f t="shared" si="5"/>
         <v>654</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B119, $C$2:$C$709, C119, $D$2:$D$709, D119, $E$2:$E$709, E119) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="11">
         <v>46243.375</v>
       </c>
@@ -6891,17 +6887,17 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M120" s="18">
-        <f>ABS((D120*E120)-L120)</f>
+        <f t="shared" si="5"/>
         <v>710.99999999999636</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B120, $C$2:$C$709, C120, $D$2:$D$709, D120, $E$2:$E$709, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O120" s="10"/>
       <c r="P120"/>
     </row>
-    <row r="121" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="3">
         <v>46261.375</v>
       </c>
@@ -6939,17 +6935,17 @@
         <v>17150</v>
       </c>
       <c r="M121" s="18">
-        <f>ABS((D121*E121)-L121)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B121, $C$2:$C$709, C121, $D$2:$D$709, D121, $E$2:$E$709, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="10"/>
       <c r="P121" s="10"/>
     </row>
-    <row r="122" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3">
         <v>46276.375</v>
       </c>
@@ -6987,15 +6983,15 @@
         <v>8700</v>
       </c>
       <c r="M122" s="18">
-        <f>ABS((D122*E122)-L122)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B122, $C$2:$C$709, C122, $D$2:$D$709, D122, $E$2:$E$709, E122) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3">
         <v>46276.4</v>
       </c>
@@ -7033,15 +7029,15 @@
         <v>14200</v>
       </c>
       <c r="M123" s="18">
-        <f>ABS((D123*E123)-L123)</f>
+        <f t="shared" si="5"/>
         <v>500</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B123, $C$2:$C$709, C123, $D$2:$D$709, D123, $E$2:$E$709, E123) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -7079,15 +7075,15 @@
         <v>5905</v>
       </c>
       <c r="M124" s="18">
-        <f>ABS((D124*E124)-L124)</f>
+        <f t="shared" si="5"/>
         <v>275</v>
       </c>
       <c r="N124" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B124, $C$2:$C$709, C124, $D$2:$D$709, D124, $E$2:$E$709, E124) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -7117,7 +7113,7 @@
       </c>
       <c r="J125" s="35"/>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B125, $C$2:$C$709, C125, $D$2:$D$709, D125, $E$2:$E$709, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O125" s="39" t="s">
@@ -7125,7 +7121,7 @@
       </c>
       <c r="P125"/>
     </row>
-    <row r="126" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="3">
         <v>46269.614583333336</v>
       </c>
@@ -7167,14 +7163,14 @@
         <v>280</v>
       </c>
       <c r="N126" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B126, $C$2:$C$709, C126, $D$2:$D$709, D126, $E$2:$E$709, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="127" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3">
         <v>46274.375</v>
       </c>
@@ -7216,11 +7212,11 @@
         <v>300</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B127, $C$2:$C$709, C127, $D$2:$D$709, D127, $E$2:$E$709, E127) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="11">
         <v>46252.645833333336</v>
       </c>
@@ -7250,12 +7246,12 @@
       </c>
       <c r="J128" s="35"/>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B128, $C$2:$C$709, C128, $D$2:$D$709, D128, $E$2:$E$709, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="24"/>
     </row>
-    <row r="129" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="8" t="s">
         <v>62</v>
       </c>
@@ -7287,11 +7283,11 @@
         <v>118</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B129, $C$2:$C$709, C129, $D$2:$D$709, D129, $E$2:$E$709, E129) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -7333,14 +7329,14 @@
         <v>48320</v>
       </c>
       <c r="N130" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B130, $C$2:$C$709, C130, $D$2:$D$709, D130, $E$2:$E$709, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="6">IF(COUNTIFS( $B$2:$B$709, B130, $C$2:$C$709, C130, $D$2:$D$709, D130, $E$2:$E$709, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="3">
         <v>46266.375</v>
       </c>
@@ -7382,12 +7378,12 @@
         <v>300</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B131, $C$2:$C$709, C131, $D$2:$D$709, D131, $E$2:$E$709, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P131" s="30"/>
     </row>
-    <row r="132" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="11">
         <v>46243.375</v>
       </c>
@@ -7429,14 +7425,14 @@
         <v>650</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B132, $C$2:$C$709, C132, $D$2:$D$709, D132, $E$2:$E$709, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O132" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="133" spans="1:16" s="30" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:16" s="30" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="3">
         <v>46274.375</v>
       </c>
@@ -7478,13 +7474,13 @@
         <v>250</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B133, $C$2:$C$709, C133, $D$2:$D$709, D133, $E$2:$E$709, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O133" s="10"/>
       <c r="P133" s="10"/>
     </row>
-    <row r="134" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="11">
         <v>46253.375</v>
       </c>
@@ -7519,11 +7515,11 @@
         <v>145</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B134, $C$2:$C$709, C134, $D$2:$D$709, D134, $E$2:$E$709, E134) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3">
         <v>46261.375</v>
       </c>
@@ -7561,16 +7557,16 @@
         <v>14440</v>
       </c>
       <c r="M135" s="18">
-        <f>ABS((D135*E135)-L135)</f>
+        <f t="shared" ref="M135:M144" si="7">ABS((D135*E135)-L135)</f>
         <v>300</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B135, $C$2:$C$709, C135, $D$2:$D$709, D135, $E$2:$E$709, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O135"/>
     </row>
-    <row r="136" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3">
         <v>46281.375</v>
       </c>
@@ -7608,18 +7604,18 @@
         <v>16500</v>
       </c>
       <c r="M136" s="18">
-        <f>ABS((D136*E136)-L136)</f>
+        <f t="shared" si="7"/>
         <v>1400</v>
       </c>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B136, $C$2:$C$709, C136, $D$2:$D$709, D136, $E$2:$E$709, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O136" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="137" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3">
         <v>46276.390277777777</v>
       </c>
@@ -7657,15 +7653,15 @@
         <v>14400</v>
       </c>
       <c r="M137" s="18">
-        <f>ABS((D137*E137)-L137)</f>
+        <f t="shared" si="7"/>
         <v>500</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B137, $C$2:$C$709, C137, $D$2:$D$709, D137, $E$2:$E$709, E137) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -7703,11 +7699,11 @@
         <v>18800</v>
       </c>
       <c r="M138" s="18">
-        <f>ABS((D138*E138)-L138)</f>
+        <f t="shared" si="7"/>
         <v>500</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B138, $C$2:$C$709, C138, $D$2:$D$709, D138, $E$2:$E$709, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="40" t="s">
@@ -7715,7 +7711,7 @@
       </c>
       <c r="P138" s="10"/>
     </row>
-    <row r="139" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="31">
         <v>46260.556944444441</v>
       </c>
@@ -7753,15 +7749,15 @@
         <v>6105</v>
       </c>
       <c r="M139" s="28">
-        <f>ABS((D139*E139)-L139)</f>
+        <f t="shared" si="7"/>
         <v>150</v>
       </c>
       <c r="N139" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B139, $C$2:$C$709, C139, $D$2:$D$709, D139, $E$2:$E$709, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="140" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="31">
         <v>46261.375</v>
       </c>
@@ -7799,15 +7795,15 @@
         <v>6005</v>
       </c>
       <c r="M140" s="28">
-        <f>ABS((D140*E140)-L140)</f>
+        <f t="shared" si="7"/>
         <v>250</v>
       </c>
       <c r="N140" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B140, $C$2:$C$709, C140, $D$2:$D$709, D140, $E$2:$E$709, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="141" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -7845,15 +7841,15 @@
         <v>9470</v>
       </c>
       <c r="M141" s="18">
-        <f>ABS((D141*E141)-L141)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B141, $C$2:$C$709, C141, $D$2:$D$709, D141, $E$2:$E$709, E141) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="31">
         <v>46335.62777777778</v>
       </c>
@@ -7881,7 +7877,7 @@
       <c r="I142" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J142" s="62" t="s">
+      <c r="J142" s="28" t="s">
         <v>118</v>
       </c>
       <c r="K142" s="28" t="s">
@@ -7891,17 +7887,17 @@
         <v>5370</v>
       </c>
       <c r="M142" s="28">
-        <f>ABS((D142*E142)-L142)</f>
+        <f t="shared" si="7"/>
         <v>320</v>
       </c>
       <c r="N142" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B142, $C$2:$C$709, C142, $D$2:$D$709, D142, $E$2:$E$709, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O142" s="30"/>
       <c r="P142" s="30"/>
     </row>
-    <row r="143" spans="1:16" s="25" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:16" s="25" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="31">
         <v>46280.375694444447</v>
       </c>
@@ -7939,17 +7935,17 @@
         <v>2610</v>
       </c>
       <c r="M143" s="28">
-        <f>ABS((D143*E143)-L143)</f>
+        <f t="shared" si="7"/>
         <v>235</v>
       </c>
       <c r="N143" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B143, $C$2:$C$709, C143, $D$2:$D$709, D143, $E$2:$E$709, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="30"/>
       <c r="P143" s="30"/>
     </row>
-    <row r="144" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="3">
         <v>46262.375</v>
       </c>
@@ -7987,16 +7983,16 @@
         <v>10410</v>
       </c>
       <c r="M144" s="18">
-        <f>ABS((D144*E144)-L144)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B144, $C$2:$C$709, C144, $D$2:$D$709, D144, $E$2:$E$709, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O144" s="30"/>
     </row>
-    <row r="145" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -8028,15 +8024,13 @@
         <v>118</v>
       </c>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B145, $C$2:$C$709, C145, $D$2:$D$709, D145, $E$2:$E$709, E145) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O145" s="39" t="s">
-        <v>242</v>
-      </c>
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+      <c r="O145" s="65"/>
       <c r="P145"/>
     </row>
-    <row r="146" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="3">
         <v>46261.615277777775</v>
       </c>
@@ -8078,7 +8072,7 @@
         <v>501</v>
       </c>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B146, $C$2:$C$709, C146, $D$2:$D$709, D146, $E$2:$E$709, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="39" t="s">
@@ -8086,7 +8080,7 @@
       </c>
       <c r="P146" s="10"/>
     </row>
-    <row r="147" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="11">
         <v>46252.6875</v>
       </c>
@@ -8118,11 +8112,11 @@
         <v>118</v>
       </c>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B147, $C$2:$C$709, C147, $D$2:$D$709, D147, $E$2:$E$709, E147) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -8152,12 +8146,12 @@
       </c>
       <c r="J148" s="35"/>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B148, $C$2:$C$709, C148, $D$2:$D$709, D148, $E$2:$E$709, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O148" s="30"/>
     </row>
-    <row r="149" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -8195,18 +8189,18 @@
         <v>73800</v>
       </c>
       <c r="M149" s="18">
-        <f>ABS((D149*E149)-L149)</f>
+        <f t="shared" ref="M149:M162" si="8">ABS((D149*E149)-L149)</f>
         <v>47900</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B149, $C$2:$C$709, C149, $D$2:$D$709, D149, $E$2:$E$709, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O149" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="150" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="31">
         <v>46265.375694444447</v>
       </c>
@@ -8244,15 +8238,15 @@
         <v>7578</v>
       </c>
       <c r="M150" s="28">
-        <f>ABS((D150*E150)-L150)</f>
+        <f t="shared" si="8"/>
         <v>294</v>
       </c>
       <c r="N150" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B150, $C$2:$C$709, C150, $D$2:$D$709, D150, $E$2:$E$709, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="151" spans="1:16" s="30" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:16" s="30" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="31">
         <v>46266.375694444447</v>
       </c>
@@ -8290,42 +8284,42 @@
         <v>7578</v>
       </c>
       <c r="M151" s="28">
-        <f>ABS((D151*E151)-L151)</f>
+        <f t="shared" si="8"/>
         <v>294</v>
       </c>
       <c r="N151" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B151, $C$2:$C$709, C151, $D$2:$D$709, D151, $E$2:$E$709, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O151" s="10"/>
       <c r="P151" s="10"/>
     </row>
-    <row r="152" spans="1:16" s="30" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="65">
+    <row r="152" spans="1:16" s="30" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A152" s="61">
         <v>46267.424305555556</v>
       </c>
-      <c r="B152" s="66" t="s">
+      <c r="B152" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="C152" s="66" t="s">
-        <v>7</v>
-      </c>
-      <c r="D152" s="67">
+      <c r="C152" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D152" s="63">
         <v>2</v>
       </c>
-      <c r="E152" s="67">
+      <c r="E152" s="63">
         <v>2624</v>
       </c>
-      <c r="F152" s="67">
+      <c r="F152" s="63">
         <v>10.05326511</v>
       </c>
       <c r="G152" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="H152" s="68">
+      <c r="H152" s="64">
         <v>2384.3000000000002</v>
       </c>
-      <c r="I152" s="66" t="s">
+      <c r="I152" s="62" t="s">
         <v>8</v>
       </c>
       <c r="J152" s="28" t="s">
@@ -8338,15 +8332,15 @@
         <v>4968</v>
       </c>
       <c r="M152" s="28">
-        <f>ABS((D152*E152)-L152)</f>
+        <f t="shared" si="8"/>
         <v>280</v>
       </c>
       <c r="N152" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B152, $C$2:$C$709, C152, $D$2:$D$709, D152, $E$2:$E$709, E152) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="153" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="3">
         <v>46267.375</v>
       </c>
@@ -8384,15 +8378,15 @@
         <v>4080</v>
       </c>
       <c r="M153" s="18">
-        <f>ABS((D153*E153)-L153)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B153, $C$2:$C$709, C153, $D$2:$D$709, D153, $E$2:$E$709, E153) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="154" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3">
         <v>46261.375</v>
       </c>
@@ -8430,16 +8424,16 @@
         <v>34100</v>
       </c>
       <c r="M154" s="18">
-        <f>ABS((D154*E154)-L154)</f>
+        <f t="shared" si="8"/>
         <v>1700</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B154, $C$2:$C$709, C154, $D$2:$D$709, D154, $E$2:$E$709, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O154" s="30"/>
     </row>
-    <row r="155" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="3">
         <v>46266.375</v>
       </c>
@@ -8477,18 +8471,18 @@
         <v>25300</v>
       </c>
       <c r="M155" s="18">
-        <f>ABS((D155*E155)-L155)</f>
+        <f t="shared" si="8"/>
         <v>650</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B155, $C$2:$C$709, C155, $D$2:$D$709, D155, $E$2:$E$709, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O155" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="156" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -8526,18 +8520,18 @@
         <v>12480</v>
       </c>
       <c r="M156" s="18">
-        <f>ABS((D156*E156)-L156)</f>
+        <f t="shared" si="8"/>
         <v>495</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B156, $C$2:$C$709, C156, $D$2:$D$709, D156, $E$2:$E$709, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O156" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="157" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="3">
         <v>46269.411111111112</v>
       </c>
@@ -8575,15 +8569,15 @@
         <v>18140</v>
       </c>
       <c r="M157" s="26">
-        <f>ABS((D157*E157)-L157)</f>
+        <f t="shared" si="8"/>
         <v>650</v>
       </c>
       <c r="N157" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B157, $C$2:$C$709, C157, $D$2:$D$709, D157, $E$2:$E$709, E157) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="158" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="3">
         <v>46276.388194444444</v>
       </c>
@@ -8621,15 +8615,15 @@
         <v>14650</v>
       </c>
       <c r="M158" s="18">
-        <f>ABS((D158*E158)-L158)</f>
+        <f t="shared" si="8"/>
         <v>450</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B158, $C$2:$C$709, C158, $D$2:$D$709, D158, $E$2:$E$709, E158) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="3">
         <v>46261.375</v>
       </c>
@@ -8667,15 +8661,15 @@
         <v>10510</v>
       </c>
       <c r="M159" s="18">
-        <f>ABS((D159*E159)-L159)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B159, $C$2:$C$709, C159, $D$2:$D$709, D159, $E$2:$E$709, E159) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -8713,15 +8707,15 @@
         <v>12510</v>
       </c>
       <c r="M160" s="18">
-        <f>ABS((D160*E160)-L160)</f>
+        <f t="shared" si="8"/>
         <v>290</v>
       </c>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B160, $C$2:$C$709, C160, $D$2:$D$709, D160, $E$2:$E$709, E160) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="161" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="43">
         <v>46273.385416666664</v>
       </c>
@@ -8759,11 +8753,11 @@
         <v>16580</v>
       </c>
       <c r="M161" s="45">
-        <f>ABS((D161*E161)-L161)</f>
+        <f t="shared" si="8"/>
         <v>750</v>
       </c>
       <c r="N161" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B161, $C$2:$C$709, C161, $D$2:$D$709, D161, $E$2:$E$709, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O161" s="24"/>
@@ -8771,7 +8765,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="162" spans="1:16" s="30" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:16" s="30" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="3">
         <v>46269.375</v>
       </c>
@@ -8809,17 +8803,17 @@
         <v>2105</v>
       </c>
       <c r="M162" s="26">
-        <f>ABS((D162*E162)-L162)</f>
+        <f t="shared" si="8"/>
         <v>250</v>
       </c>
       <c r="N162" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B162, $C$2:$C$709, C162, $D$2:$D$709, D162, $E$2:$E$709, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O162" s="10"/>
       <c r="P162" s="10"/>
     </row>
-    <row r="163" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="8" t="s">
         <v>62</v>
       </c>
@@ -8852,13 +8846,13 @@
       <c r="L163" s="18"/>
       <c r="M163" s="18"/>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B163, $C$2:$C$709, C163, $D$2:$D$709, D163, $E$2:$E$709, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O163" s="10"/>
       <c r="P163" s="10"/>
     </row>
-    <row r="164" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -8890,11 +8884,11 @@
         <v>117</v>
       </c>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B164, $C$2:$C$709, C164, $D$2:$D$709, D164, $E$2:$E$709, E164) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -8936,7 +8930,7 @@
         <v>300</v>
       </c>
       <c r="N165" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B165, $C$2:$C$709, C165, $D$2:$D$709, D165, $E$2:$E$709, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O165" s="39" t="s">
@@ -8944,7 +8938,7 @@
       </c>
       <c r="P165"/>
     </row>
-    <row r="166" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="3">
         <v>46265.474999999999</v>
       </c>
@@ -8986,11 +8980,11 @@
         <v>300</v>
       </c>
       <c r="N166" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B166, $C$2:$C$709, C166, $D$2:$D$709, D166, $E$2:$E$709, E166) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="167" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -9020,11 +9014,11 @@
       </c>
       <c r="J167" s="35"/>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B167, $C$2:$C$709, C167, $D$2:$D$709, D167, $E$2:$E$709, E167) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="3">
         <v>46265.390277777777</v>
       </c>
@@ -9062,17 +9056,17 @@
         <v>25530</v>
       </c>
       <c r="M168" s="18">
-        <f>ABS((D168*E168)-L168)</f>
+        <f t="shared" ref="M168:M174" si="9">ABS((D168*E168)-L168)</f>
         <v>650</v>
       </c>
       <c r="N168" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B168, $C$2:$C$709, C168, $D$2:$D$709, D168, $E$2:$E$709, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O168"/>
       <c r="P168"/>
     </row>
-    <row r="169" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="31">
         <v>46265.375694444447</v>
       </c>
@@ -9110,18 +9104,18 @@
         <v>5520</v>
       </c>
       <c r="M169" s="28">
-        <f>ABS((D169*E169)-L169)</f>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N169" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B169, $C$2:$C$709, C169, $D$2:$D$709, D169, $E$2:$E$709, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O169" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="170" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="41">
         <v>46243.505555555559</v>
       </c>
@@ -9159,18 +9153,18 @@
         <v>2657</v>
       </c>
       <c r="M170" s="28">
-        <f>ABS((D170*E170)-L170)</f>
+        <f t="shared" si="9"/>
         <v>253</v>
       </c>
       <c r="N170" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B170, $C$2:$C$709, C170, $D$2:$D$709, D170, $E$2:$E$709, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O170" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="171" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="31">
         <v>46280.588194444441</v>
       </c>
@@ -9208,11 +9202,11 @@
         <v>2554.5</v>
       </c>
       <c r="M171" s="28">
-        <f>ABS((D171*E171)-L171)</f>
+        <f t="shared" si="9"/>
         <v>355.5</v>
       </c>
       <c r="N171" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B171, $C$2:$C$709, C171, $D$2:$D$709, D171, $E$2:$E$709, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O171" s="39" t="s">
@@ -9220,7 +9214,7 @@
       </c>
       <c r="P171" s="30"/>
     </row>
-    <row r="172" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="31">
         <v>46272.451388888891</v>
       </c>
@@ -9258,17 +9252,17 @@
         <v>8820</v>
       </c>
       <c r="M172" s="28">
-        <f>ABS((D172*E172)-L172)</f>
+        <f t="shared" si="9"/>
         <v>650</v>
       </c>
       <c r="N172" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B172, $C$2:$C$709, C172, $D$2:$D$709, D172, $E$2:$E$709, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O172" s="30"/>
       <c r="P172" s="30"/>
     </row>
-    <row r="173" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="31">
         <v>46272.390972222223</v>
       </c>
@@ -9306,17 +9300,17 @@
         <v>36946</v>
       </c>
       <c r="M173" s="28">
-        <f>ABS((D173*E173)-L173)</f>
+        <f t="shared" si="9"/>
         <v>934</v>
       </c>
       <c r="N173" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B173, $C$2:$C$709, C173, $D$2:$D$709, D173, $E$2:$E$709, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O173" s="30"/>
       <c r="P173" s="30"/>
     </row>
-    <row r="174" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="3">
         <v>46335.421527777777</v>
       </c>
@@ -9354,11 +9348,11 @@
         <v>8049</v>
       </c>
       <c r="M174" s="18">
-        <f>ABS((D174*E174)-L174)</f>
+        <f t="shared" si="9"/>
         <v>800</v>
       </c>
       <c r="N174" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B174, $C$2:$C$709, C174, $D$2:$D$709, D174, $E$2:$E$709, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O174" s="39" t="s">
@@ -9366,7 +9360,7 @@
       </c>
       <c r="P174" s="10"/>
     </row>
-    <row r="175" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9396,11 +9390,11 @@
       </c>
       <c r="J175" s="35"/>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B175, $C$2:$C$709, C175, $D$2:$D$709, D175, $E$2:$E$709, E175) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="176" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9432,11 +9426,11 @@
         <v>117</v>
       </c>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B176, $C$2:$C$709, C176, $D$2:$D$709, D176, $E$2:$E$709, E176) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="31">
         <v>46258.443055555559</v>
       </c>
@@ -9478,13 +9472,13 @@
         <v>300</v>
       </c>
       <c r="N177" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B177, $C$2:$C$709, C177, $D$2:$D$709, D177, $E$2:$E$709, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O177" s="30"/>
       <c r="P177" s="30"/>
     </row>
-    <row r="178" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="31">
         <v>46259.375</v>
       </c>
@@ -9526,13 +9520,13 @@
         <v>188</v>
       </c>
       <c r="N178" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B178, $C$2:$C$709, C178, $D$2:$D$709, D178, $E$2:$E$709, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O178" s="30"/>
       <c r="P178" s="30"/>
     </row>
-    <row r="179" spans="1:16" s="30" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:16" s="30" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="34">
         <v>46255</v>
       </c>
@@ -9574,12 +9568,12 @@
         <v>140</v>
       </c>
       <c r="N179" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B179, $C$2:$C$709, C179, $D$2:$D$709, D179, $E$2:$E$709, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O179" s="10"/>
     </row>
-    <row r="180" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="31">
         <v>46261.385416666664</v>
       </c>
@@ -9621,11 +9615,11 @@
         <v>300</v>
       </c>
       <c r="N180" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B180, $C$2:$C$709, C180, $D$2:$D$709, D180, $E$2:$E$709, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="181" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="8" t="s">
         <v>62</v>
       </c>
@@ -9657,11 +9651,11 @@
         <v>195</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B181, $C$2:$C$709, C181, $D$2:$D$709, D181, $E$2:$E$709, E181) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="182" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="9" t="s">
         <v>62</v>
       </c>
@@ -9691,11 +9685,11 @@
       </c>
       <c r="J182" s="35"/>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B182, $C$2:$C$709, C182, $D$2:$D$709, D182, $E$2:$E$709, E182) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="183" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -9725,12 +9719,12 @@
       </c>
       <c r="J183" s="35"/>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B183, $C$2:$C$709, C183, $D$2:$D$709, D183, $E$2:$E$709, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P183" s="30"/>
     </row>
-    <row r="184" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -9772,11 +9766,11 @@
         <v>47480</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B184, $C$2:$C$709, C184, $D$2:$D$709, D184, $E$2:$E$709, E184) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="185" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9808,14 +9802,14 @@
         <v>118</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B185, $C$2:$C$709, C185, $D$2:$D$709, D185, $E$2:$E$709, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="186" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="8" t="s">
         <v>62</v>
       </c>
@@ -9845,11 +9839,11 @@
       </c>
       <c r="J186" s="35"/>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B186, $C$2:$C$709, C186, $D$2:$D$709, D186, $E$2:$E$709, E186) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="187" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="3">
         <v>46281.37777777778</v>
       </c>
@@ -9891,11 +9885,11 @@
         <v>810</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B187, $C$2:$C$709, C187, $D$2:$D$709, D187, $E$2:$E$709, E187) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="188" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="3">
         <v>46266.375</v>
       </c>
@@ -9937,11 +9931,11 @@
         <v>360</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B188, $C$2:$C$709, C188, $D$2:$D$709, D188, $E$2:$E$709, E188) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="189" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -9983,11 +9977,11 @@
         <v>340</v>
       </c>
       <c r="N189" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B189, $C$2:$C$709, C189, $D$2:$D$709, D189, $E$2:$E$709, E189) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="190" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="8" t="s">
         <v>62</v>
       </c>
@@ -10019,11 +10013,11 @@
         <v>117</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B190, $C$2:$C$709, C190, $D$2:$D$709, D190, $E$2:$E$709, E190) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -10065,11 +10059,11 @@
         <v>250</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B191, $C$2:$C$709, C191, $D$2:$D$709, D191, $E$2:$E$709, E191) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="192" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -10111,11 +10105,11 @@
         <v>300</v>
       </c>
       <c r="N192" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B192, $C$2:$C$709, C192, $D$2:$D$709, D192, $E$2:$E$709, E192) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="193" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -10147,11 +10141,11 @@
         <v>118</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B193, $C$2:$C$709, C193, $D$2:$D$709, D193, $E$2:$E$709, E193) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="194" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="31">
         <v>46258.443749999999</v>
       </c>
@@ -10193,13 +10187,13 @@
         <v>527.5</v>
       </c>
       <c r="N194" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B194, $C$2:$C$709, C194, $D$2:$D$709, D194, $E$2:$E$709, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="10">IF(COUNTIFS( $B$2:$B$709, B194, $C$2:$C$709, C194, $D$2:$D$709, D194, $E$2:$E$709, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O194" s="30"/>
       <c r="P194" s="30"/>
     </row>
-    <row r="195" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="41">
         <v>46253.4</v>
       </c>
@@ -10236,13 +10230,13 @@
       <c r="L195" s="28"/>
       <c r="M195" s="28"/>
       <c r="N195" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B195, $C$2:$C$709, C195, $D$2:$D$709, D195, $E$2:$E$709, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O195" s="30"/>
       <c r="P195" s="30"/>
     </row>
-    <row r="196" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="8" t="s">
         <v>62</v>
       </c>
@@ -10274,11 +10268,11 @@
         <v>117</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B196, $C$2:$C$709, C196, $D$2:$D$709, D196, $E$2:$E$709, E196) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="3">
         <v>46266.375</v>
       </c>
@@ -10320,7 +10314,7 @@
         <v>300</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B197, $C$2:$C$709, C197, $D$2:$D$709, D197, $E$2:$E$709, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O197" s="39" t="s">
@@ -10328,7 +10322,7 @@
       </c>
       <c r="P197" s="30"/>
     </row>
-    <row r="198" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="3">
         <v>46262.463194444441</v>
       </c>
@@ -10370,13 +10364,13 @@
         <v>300</v>
       </c>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B198, $C$2:$C$709, C198, $D$2:$D$709, D198, $E$2:$E$709, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O198" s="10"/>
       <c r="P198" s="10"/>
     </row>
-    <row r="199" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="3">
         <v>46276.375</v>
       </c>
@@ -10418,11 +10412,11 @@
         <v>816</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B199, $C$2:$C$709, C199, $D$2:$D$709, D199, $E$2:$E$709, E199) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="200" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -10454,11 +10448,11 @@
         <v>117</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B200, $C$2:$C$709, C200, $D$2:$D$709, D200, $E$2:$E$709, E200) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="201" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="3">
         <v>46274.414583333331</v>
       </c>
@@ -10500,14 +10494,14 @@
         <v>646</v>
       </c>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B201, $C$2:$C$709, C201, $D$2:$D$709, D201, $E$2:$E$709, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O201" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="202" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -10549,11 +10543,11 @@
         <v>260</v>
       </c>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B202, $C$2:$C$709, C202, $D$2:$D$709, D202, $E$2:$E$709, E202) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="203" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="44" t="s">
         <v>62</v>
       </c>
@@ -10588,7 +10582,7 @@
       <c r="L203" s="45"/>
       <c r="M203" s="45"/>
       <c r="N203" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B203, $C$2:$C$709, C203, $D$2:$D$709, D203, $E$2:$E$709, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O203" s="24"/>
@@ -10596,7 +10590,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="204" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -10638,14 +10632,14 @@
         <v>880</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B204, $C$2:$C$709, C204, $D$2:$D$709, D204, $E$2:$E$709, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O204" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="205" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="3">
         <v>46262.375</v>
       </c>
@@ -10687,11 +10681,11 @@
         <v>300</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B205, $C$2:$C$709, C205, $D$2:$D$709, D205, $E$2:$E$709, E205) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="206" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="3">
         <v>46260.425694444442</v>
       </c>
@@ -10733,12 +10727,12 @@
         <v>1000</v>
       </c>
       <c r="N206" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B206, $C$2:$C$709, C206, $D$2:$D$709, D206, $E$2:$E$709, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P206" s="30"/>
     </row>
-    <row r="207" spans="1:16" s="30" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:16" s="30" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="3">
         <v>46276.375</v>
       </c>
@@ -10780,13 +10774,13 @@
         <v>450</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B207, $C$2:$C$709, C207, $D$2:$D$709, D207, $E$2:$E$709, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O207" s="10"/>
       <c r="P207" s="10"/>
     </row>
-    <row r="208" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="8" t="s">
         <v>62</v>
       </c>
@@ -10818,12 +10812,12 @@
         <v>118</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B208, $C$2:$C$709, C208, $D$2:$D$709, D208, $E$2:$E$709, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O208" s="30"/>
     </row>
-    <row r="209" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -10865,12 +10859,12 @@
         <v>250</v>
       </c>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B209, $C$2:$C$709, C209, $D$2:$D$709, D209, $E$2:$E$709, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P209" s="30"/>
     </row>
-    <row r="210" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -10907,11 +10901,11 @@
       <c r="L210" s="17"/>
       <c r="M210" s="17"/>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B210, $C$2:$C$709, C210, $D$2:$D$709, D210, $E$2:$E$709, E210) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="211" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="3">
         <v>46274.375</v>
       </c>
@@ -10953,11 +10947,11 @@
         <v>651</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B211, $C$2:$C$709, C211, $D$2:$D$709, D211, $E$2:$E$709, E211) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="212" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="11">
         <v>46243.375</v>
       </c>
@@ -10999,12 +10993,12 @@
         <v>300</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B212, $C$2:$C$709, C212, $D$2:$D$709, D212, $E$2:$E$709, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P212" s="25"/>
     </row>
-    <row r="213" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="8" t="s">
         <v>62</v>
       </c>
@@ -11036,11 +11030,11 @@
         <v>55</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B213, $C$2:$C$709, C213, $D$2:$D$709, D213, $E$2:$E$709, E213) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="214" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="8" t="s">
         <v>62</v>
       </c>
@@ -11072,11 +11066,11 @@
         <v>118</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B214, $C$2:$C$709, C214, $D$2:$D$709, D214, $E$2:$E$709, E214) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="215" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -11118,11 +11112,11 @@
         <v>400</v>
       </c>
       <c r="N215" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B215, $C$2:$C$709, C215, $D$2:$D$709, D215, $E$2:$E$709, E215) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="216" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -11154,11 +11148,11 @@
         <v>55</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B216, $C$2:$C$709, C216, $D$2:$D$709, D216, $E$2:$E$709, E216) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="217" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="8" t="s">
         <v>62</v>
       </c>
@@ -11188,11 +11182,11 @@
       </c>
       <c r="J217" s="35"/>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B217, $C$2:$C$709, C217, $D$2:$D$709, D217, $E$2:$E$709, E217) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="218" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="8" t="s">
         <v>62</v>
       </c>
@@ -11222,11 +11216,11 @@
       </c>
       <c r="J218" s="35"/>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B218, $C$2:$C$709, C218, $D$2:$D$709, D218, $E$2:$E$709, E218) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="219" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="8" t="s">
         <v>62</v>
       </c>
@@ -11258,11 +11252,11 @@
         <v>117</v>
       </c>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B219, $C$2:$C$709, C219, $D$2:$D$709, D219, $E$2:$E$709, E219) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="220" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="8" t="s">
         <v>62</v>
       </c>
@@ -11294,11 +11288,11 @@
         <v>118</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B220, $C$2:$C$709, C220, $D$2:$D$709, D220, $E$2:$E$709, E220) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="221" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -11340,11 +11334,11 @@
         <v>940</v>
       </c>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B221, $C$2:$C$709, C221, $D$2:$D$709, D221, $E$2:$E$709, E221) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="222" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="11">
         <v>46252.6875</v>
       </c>
@@ -11376,11 +11370,11 @@
         <v>154</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B222, $C$2:$C$709, C222, $D$2:$D$709, D222, $E$2:$E$709, E222) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="223" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="8" t="s">
         <v>62</v>
       </c>
@@ -11410,11 +11404,11 @@
       </c>
       <c r="J223" s="35"/>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B223, $C$2:$C$709, C223, $D$2:$D$709, D223, $E$2:$E$709, E223) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="224" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="8" t="s">
         <v>62</v>
       </c>
@@ -11446,12 +11440,12 @@
         <v>118</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B224, $C$2:$C$709, C224, $D$2:$D$709, D224, $E$2:$E$709, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O224" s="30"/>
     </row>
-    <row r="225" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="8" t="s">
         <v>62</v>
       </c>
@@ -11481,11 +11475,11 @@
       </c>
       <c r="J225" s="35"/>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B225, $C$2:$C$709, C225, $D$2:$D$709, D225, $E$2:$E$709, E225) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="226" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="8" t="s">
         <v>62</v>
       </c>
@@ -11517,11 +11511,11 @@
         <v>118</v>
       </c>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B226, $C$2:$C$709, C226, $D$2:$D$709, D226, $E$2:$E$709, E226) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="227" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="3">
         <v>46265.460416666669</v>
       </c>
@@ -11563,12 +11557,12 @@
         <v>650</v>
       </c>
       <c r="N227" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B227, $C$2:$C$709, C227, $D$2:$D$709, D227, $E$2:$E$709, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P227" s="30"/>
     </row>
-    <row r="228" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="8" t="s">
         <v>62</v>
       </c>
@@ -11598,11 +11592,11 @@
       </c>
       <c r="J228" s="35"/>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B228, $C$2:$C$709, C228, $D$2:$D$709, D228, $E$2:$E$709, E228) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="229" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="8" t="s">
         <v>62</v>
       </c>
@@ -11634,12 +11628,12 @@
         <v>117</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B229, $C$2:$C$709, C229, $D$2:$D$709, D229, $E$2:$E$709, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P229" s="30"/>
     </row>
-    <row r="230" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="11">
         <v>46252.6875</v>
       </c>
@@ -11671,11 +11665,11 @@
         <v>117</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B230, $C$2:$C$709, C230, $D$2:$D$709, D230, $E$2:$E$709, E230) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="231" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="8" t="s">
         <v>62</v>
       </c>
@@ -11705,11 +11699,11 @@
       </c>
       <c r="J231" s="35"/>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B231, $C$2:$C$709, C231, $D$2:$D$709, D231, $E$2:$E$709, E231) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="232" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="232" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="11">
         <v>46252.6875</v>
       </c>
@@ -11741,11 +11735,11 @@
         <v>117</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B232, $C$2:$C$709, C232, $D$2:$D$709, D232, $E$2:$E$709, E232) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="233" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -11780,11 +11774,11 @@
         <v>146</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B233, $C$2:$C$709, C233, $D$2:$D$709, D233, $E$2:$E$709, E233) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="3">
         <v>46268.375</v>
       </c>
@@ -11826,11 +11820,11 @@
         <v>1800</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B234, $C$2:$C$709, C234, $D$2:$D$709, D234, $E$2:$E$709, E234) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="3">
         <v>46262.375</v>
       </c>
@@ -11872,12 +11866,12 @@
         <v>370</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B235, $C$2:$C$709, C235, $D$2:$D$709, D235, $E$2:$E$709, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P235" s="30"/>
     </row>
-    <row r="236" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="8" t="s">
         <v>62</v>
       </c>
@@ -11909,11 +11903,11 @@
         <v>117</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B236, $C$2:$C$709, C236, $D$2:$D$709, D236, $E$2:$E$709, E236) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="237" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="3">
         <v>46269.643055555556</v>
       </c>
@@ -11955,11 +11949,11 @@
         <v>268</v>
       </c>
       <c r="N237" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B237, $C$2:$C$709, C237, $D$2:$D$709, D237, $E$2:$E$709, E237) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="238" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="3">
         <v>46262.375</v>
       </c>
@@ -12001,11 +11995,11 @@
         <v>320</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B238, $C$2:$C$709, C238, $D$2:$D$709, D238, $E$2:$E$709, E238) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="239" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="3">
         <v>46265.486111111109</v>
       </c>
@@ -12047,11 +12041,11 @@
         <v>448</v>
       </c>
       <c r="N239" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B239, $C$2:$C$709, C239, $D$2:$D$709, D239, $E$2:$E$709, E239) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="240" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="8" t="s">
         <v>62</v>
       </c>
@@ -12083,11 +12077,11 @@
         <v>118</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B240, $C$2:$C$709, C240, $D$2:$D$709, D240, $E$2:$E$709, E240) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="241" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="8" t="s">
         <v>62</v>
       </c>
@@ -12117,11 +12111,11 @@
       </c>
       <c r="J241" s="35"/>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B241, $C$2:$C$709, C241, $D$2:$D$709, D241, $E$2:$E$709, E241) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="242" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -12163,14 +12157,14 @@
         <v>500</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B242, $C$2:$C$709, C242, $D$2:$D$709, D242, $E$2:$E$709, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O242" s="39" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="243" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="3">
         <v>46260.375</v>
       </c>
@@ -12212,12 +12206,12 @@
         <v>650</v>
       </c>
       <c r="N243" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B243, $C$2:$C$709, C243, $D$2:$D$709, D243, $E$2:$E$709, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P243" s="30"/>
     </row>
-    <row r="244" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="3">
         <v>46262.375</v>
       </c>
@@ -12259,11 +12253,11 @@
         <v>300</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B244, $C$2:$C$709, C244, $D$2:$D$709, D244, $E$2:$E$709, E244) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="245" spans="1:16" s="30" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" s="30" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="3">
         <v>46266.509722222225</v>
       </c>
@@ -12305,13 +12299,13 @@
         <v>300</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B245, $C$2:$C$709, C245, $D$2:$D$709, D245, $E$2:$E$709, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="10"/>
       <c r="P245" s="10"/>
     </row>
-    <row r="246" spans="1:16" s="30" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:16" s="30" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -12344,12 +12338,12 @@
       <c r="L246" s="18"/>
       <c r="M246" s="18"/>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B246, $C$2:$C$709, C246, $D$2:$D$709, D246, $E$2:$E$709, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P246" s="10"/>
     </row>
-    <row r="247" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -12391,11 +12385,11 @@
         <v>250</v>
       </c>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B247, $C$2:$C$709, C247, $D$2:$D$709, D247, $E$2:$E$709, E247) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="248" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="8" t="s">
         <v>62</v>
       </c>
@@ -12427,11 +12421,11 @@
         <v>118</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B248, $C$2:$C$709, C248, $D$2:$D$709, D248, $E$2:$E$709, E248) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="249" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="3">
         <v>46260.375</v>
       </c>
@@ -12473,11 +12467,11 @@
         <v>800</v>
       </c>
       <c r="N249" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B249, $C$2:$C$709, C249, $D$2:$D$709, D249, $E$2:$E$709, E249) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="250" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="8" t="s">
         <v>62</v>
       </c>
@@ -12507,11 +12501,11 @@
       </c>
       <c r="J250" s="35"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B250, $C$2:$C$709, C250, $D$2:$D$709, D250, $E$2:$E$709, E250) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="251" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="8" t="s">
         <v>62</v>
       </c>
@@ -12541,11 +12535,11 @@
       </c>
       <c r="J251" s="35"/>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B251, $C$2:$C$709, C251, $D$2:$D$709, D251, $E$2:$E$709, E251) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="252" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -12575,11 +12569,11 @@
       </c>
       <c r="J252" s="35"/>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B252, $C$2:$C$709, C252, $D$2:$D$709, D252, $E$2:$E$709, E252) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="253" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="3">
         <v>46260.634027777778</v>
       </c>
@@ -12621,11 +12615,11 @@
         <v>480</v>
       </c>
       <c r="N253" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B253, $C$2:$C$709, C253, $D$2:$D$709, D253, $E$2:$E$709, E253) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="11">
         <v>46252.6875</v>
       </c>
@@ -12657,11 +12651,11 @@
         <v>117</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B254, $C$2:$C$709, C254, $D$2:$D$709, D254, $E$2:$E$709, E254) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="255" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="11">
         <v>46252.6875</v>
       </c>
@@ -12693,12 +12687,12 @@
         <v>118</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B255, $C$2:$C$709, C255, $D$2:$D$709, D255, $E$2:$E$709, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O255" s="30"/>
     </row>
-    <row r="256" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="3">
         <v>46260.554861111108</v>
       </c>
@@ -12740,11 +12734,11 @@
         <v>250</v>
       </c>
       <c r="N256" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B256, $C$2:$C$709, C256, $D$2:$D$709, D256, $E$2:$E$709, E256) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="257" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="8" t="s">
         <v>62</v>
       </c>
@@ -12776,11 +12770,11 @@
         <v>117</v>
       </c>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B257, $C$2:$C$709, C257, $D$2:$D$709, D257, $E$2:$E$709, E257) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="258" spans="1:16" s="30" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" s="30" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="8" t="s">
         <v>62</v>
       </c>
@@ -12813,13 +12807,13 @@
       <c r="L258" s="18"/>
       <c r="M258" s="18"/>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B258, $C$2:$C$709, C258, $D$2:$D$709, D258, $E$2:$E$709, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N295" si="11">IF(COUNTIFS( $B$2:$B$709, B258, $C$2:$C$709, C258, $D$2:$D$709, D258, $E$2:$E$709, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O258" s="10"/>
       <c r="P258" s="10"/>
     </row>
-    <row r="259" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="8" t="s">
         <v>62</v>
       </c>
@@ -12851,11 +12845,11 @@
         <v>118</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B259, $C$2:$C$709, C259, $D$2:$D$709, D259, $E$2:$E$709, E259) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="260" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="3">
         <v>46259.375</v>
       </c>
@@ -12897,12 +12891,12 @@
         <v>650</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B260, $C$2:$C$709, C260, $D$2:$D$709, D260, $E$2:$E$709, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="30"/>
     </row>
-    <row r="261" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="20">
         <v>46255</v>
       </c>
@@ -12944,11 +12938,11 @@
         <v>300</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B261, $C$2:$C$709, C261, $D$2:$D$709, D261, $E$2:$E$709, E261) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="262" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="3">
         <v>46265.415277777778</v>
       </c>
@@ -12990,13 +12984,13 @@
         <v>285</v>
       </c>
       <c r="N262" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B262, $C$2:$C$709, C262, $D$2:$D$709, D262, $E$2:$E$709, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O262" s="10"/>
       <c r="P262" s="10"/>
     </row>
-    <row r="263" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="3">
         <v>46266.375</v>
       </c>
@@ -13038,11 +13032,11 @@
         <v>726</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B263, $C$2:$C$709, C263, $D$2:$D$709, D263, $E$2:$E$709, E263) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="264" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="8" t="s">
         <v>62</v>
       </c>
@@ -13072,11 +13066,11 @@
       </c>
       <c r="J264" s="35"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B264, $C$2:$C$709, C264, $D$2:$D$709, D264, $E$2:$E$709, E264) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="265" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="8" t="s">
         <v>62</v>
       </c>
@@ -13108,11 +13102,11 @@
         <v>118</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B265, $C$2:$C$709, C265, $D$2:$D$709, D265, $E$2:$E$709, E265) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="266" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="3">
         <v>46261.375</v>
       </c>
@@ -13154,11 +13148,11 @@
         <v>260</v>
       </c>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B266, $C$2:$C$709, C266, $D$2:$D$709, D266, $E$2:$E$709, E266) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="267" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="8" t="s">
         <v>62</v>
       </c>
@@ -13193,13 +13187,13 @@
       <c r="L267" s="18"/>
       <c r="M267" s="18"/>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B267, $C$2:$C$709, C267, $D$2:$D$709, D267, $E$2:$E$709, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O267" s="10"/>
       <c r="P267" s="10"/>
     </row>
-    <row r="268" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="3">
         <v>46260.375</v>
       </c>
@@ -13241,13 +13235,13 @@
         <v>300</v>
       </c>
       <c r="N268" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B268, $C$2:$C$709, C268, $D$2:$D$709, D268, $E$2:$E$709, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O268" s="10"/>
       <c r="P268" s="10"/>
     </row>
-    <row r="269" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="8" t="s">
         <v>62</v>
       </c>
@@ -13277,11 +13271,11 @@
       </c>
       <c r="J269" s="35"/>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B269, $C$2:$C$709, C269, $D$2:$D$709, D269, $E$2:$E$709, E269) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="270" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="8" t="s">
         <v>62</v>
       </c>
@@ -13311,11 +13305,11 @@
       </c>
       <c r="J270" s="35"/>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B270, $C$2:$C$709, C270, $D$2:$D$709, D270, $E$2:$E$709, E270) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="271" spans="1:16" s="30" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16" s="30" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="8" t="s">
         <v>62</v>
       </c>
@@ -13348,12 +13342,12 @@
       <c r="L271" s="18"/>
       <c r="M271" s="18"/>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B271, $C$2:$C$709, C271, $D$2:$D$709, D271, $E$2:$E$709, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P271" s="10"/>
     </row>
-    <row r="272" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="8" t="s">
         <v>62</v>
       </c>
@@ -13385,11 +13379,11 @@
         <v>117</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B272, $C$2:$C$709, C272, $D$2:$D$709, D272, $E$2:$E$709, E272) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -13431,11 +13425,11 @@
         <v>275</v>
       </c>
       <c r="N273" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B273, $C$2:$C$709, C273, $D$2:$D$709, D273, $E$2:$E$709, E273) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="274" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="274" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="8" t="s">
         <v>62</v>
       </c>
@@ -13468,13 +13462,13 @@
       <c r="L274" s="18"/>
       <c r="M274" s="18"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B274, $C$2:$C$709, C274, $D$2:$D$709, D274, $E$2:$E$709, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O274" s="10"/>
       <c r="P274" s="10"/>
     </row>
-    <row r="275" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="8" t="s">
         <v>62</v>
       </c>
@@ -13507,13 +13501,13 @@
       <c r="L275" s="18"/>
       <c r="M275" s="18"/>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B275, $C$2:$C$709, C275, $D$2:$D$709, D275, $E$2:$E$709, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O275" s="10"/>
       <c r="P275" s="10"/>
     </row>
-    <row r="276" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="8" t="s">
         <v>62</v>
       </c>
@@ -13543,11 +13537,11 @@
       </c>
       <c r="J276" s="35"/>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B276, $C$2:$C$709, C276, $D$2:$D$709, D276, $E$2:$E$709, E276) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="277" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="3">
         <v>46260.557638888888</v>
       </c>
@@ -13589,12 +13583,12 @@
         <v>250</v>
       </c>
       <c r="N277" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B277, $C$2:$C$709, C277, $D$2:$D$709, D277, $E$2:$E$709, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P277" s="30"/>
     </row>
-    <row r="278" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="11">
         <v>46252.6875</v>
       </c>
@@ -13626,11 +13620,11 @@
         <v>118</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B278, $C$2:$C$709, C278, $D$2:$D$709, D278, $E$2:$E$709, E278) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="279" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="11">
         <v>46252.6875</v>
       </c>
@@ -13662,11 +13656,11 @@
         <v>118</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B279, $C$2:$C$709, C279, $D$2:$D$709, D279, $E$2:$E$709, E279) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="280" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="8" t="s">
         <v>62</v>
       </c>
@@ -13696,12 +13690,12 @@
       </c>
       <c r="J280" s="35"/>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B280, $C$2:$C$709, C280, $D$2:$D$709, D280, $E$2:$E$709, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P280" s="30"/>
     </row>
-    <row r="281" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="8" t="s">
         <v>62</v>
       </c>
@@ -13733,11 +13727,11 @@
         <v>118</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B281, $C$2:$C$709, C281, $D$2:$D$709, D281, $E$2:$E$709, E281) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="282" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="11">
         <v>46252.6875</v>
       </c>
@@ -13769,11 +13763,11 @@
         <v>118</v>
       </c>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B282, $C$2:$C$709, C282, $D$2:$D$709, D282, $E$2:$E$709, E282) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="283" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="283" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="8" t="s">
         <v>62</v>
       </c>
@@ -13803,11 +13797,11 @@
       </c>
       <c r="J283" s="35"/>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B283, $C$2:$C$709, C283, $D$2:$D$709, D283, $E$2:$E$709, E283) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="284" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="284" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="8" t="s">
         <v>62</v>
       </c>
@@ -13837,12 +13831,12 @@
       </c>
       <c r="J284" s="35"/>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B284, $C$2:$C$709, C284, $D$2:$D$709, D284, $E$2:$E$709, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="P284" s="30"/>
     </row>
-    <row r="285" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="3">
         <v>46260.550694444442</v>
       </c>
@@ -13884,11 +13878,11 @@
         <v>300</v>
       </c>
       <c r="N285" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B285, $C$2:$C$709, C285, $D$2:$D$709, D285, $E$2:$E$709, E285) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="286" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="8" t="s">
         <v>62</v>
       </c>
@@ -13918,11 +13912,11 @@
       </c>
       <c r="J286" s="35"/>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B286, $C$2:$C$709, C286, $D$2:$D$709, D286, $E$2:$E$709, E286) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="287" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="3">
         <v>46259.532638888886</v>
       </c>
@@ -13964,11 +13958,11 @@
         <v>250</v>
       </c>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B287, $C$2:$C$709, C287, $D$2:$D$709, D287, $E$2:$E$709, E287) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -14000,11 +13994,11 @@
         <v>55</v>
       </c>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B288, $C$2:$C$709, C288, $D$2:$D$709, D288, $E$2:$E$709, E288) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="289" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="8" t="s">
         <v>62</v>
       </c>
@@ -14034,11 +14028,11 @@
       </c>
       <c r="J289" s="35"/>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B289, $C$2:$C$709, C289, $D$2:$D$709, D289, $E$2:$E$709, E289) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="290" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="8" t="s">
         <v>62</v>
       </c>
@@ -14068,11 +14062,11 @@
       </c>
       <c r="J290" s="35"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B290, $C$2:$C$709, C290, $D$2:$D$709, D290, $E$2:$E$709, E290) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="291" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="11"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="8" t="s">
         <v>62</v>
       </c>
@@ -14107,13 +14101,13 @@
       <c r="L291" s="18"/>
       <c r="M291" s="18"/>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B291, $C$2:$C$709, C291, $D$2:$D$709, D291, $E$2:$E$709, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O291" s="10"/>
       <c r="P291" s="10"/>
     </row>
-    <row r="292" spans="1:16" s="30" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:16" s="30" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="8" t="s">
         <v>62</v>
       </c>
@@ -14146,13 +14140,13 @@
       <c r="L292" s="18"/>
       <c r="M292" s="18"/>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B292, $C$2:$C$709, C292, $D$2:$D$709, D292, $E$2:$E$709, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O292" s="10"/>
       <c r="P292" s="10"/>
     </row>
-    <row r="293" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="42" t="s">
         <v>62</v>
       </c>
@@ -14187,13 +14181,13 @@
       <c r="L293" s="28"/>
       <c r="M293" s="28"/>
       <c r="N293" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B293, $C$2:$C$709, C293, $D$2:$D$709, D293, $E$2:$E$709, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O293" s="30"/>
       <c r="P293" s="30"/>
     </row>
-    <row r="294" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="41">
         <v>46251.506249999999</v>
       </c>
@@ -14228,13 +14222,13 @@
       <c r="L294" s="28"/>
       <c r="M294" s="28"/>
       <c r="N294" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B294, $C$2:$C$709, C294, $D$2:$D$709, D294, $E$2:$E$709, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
       <c r="O294" s="30"/>
       <c r="P294" s="30"/>
     </row>
-    <row r="295" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="8" t="s">
         <v>62</v>
       </c>
@@ -14266,7 +14260,7 @@
         <v>117</v>
       </c>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B295, $C$2:$C$709, C295, $D$2:$D$709, D295, $E$2:$E$709, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="11"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21861,19 +21855,6 @@
       <c r="I985" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P295" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="B"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="14">
-      <filters blank="1"/>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P95">
-      <sortCondition descending="1" ref="F1:F295"/>
-    </sortState>
-  </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -22194,7 +22175,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B2, $C$2:$C$709, C2, $D$2:$D$709, D2, $E$2:$E$709, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$709, B2, $C$2:$C$709, C2, $D$2:$D$709, D2, $E$2:$E$709, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -22235,7 +22216,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B3, $C$2:$C$709, C3, $D$2:$D$709, D3, $E$2:$E$709, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -22276,7 +22257,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B4, $C$2:$C$709, C4, $D$2:$D$709, D4, $E$2:$E$709, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -22324,7 +22305,7 @@
         <v>34175</v>
       </c>
       <c r="N5" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B5, $C$2:$C$709, C5, $D$2:$D$709, D5, $E$2:$E$709, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -22365,7 +22346,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B6, $C$2:$C$709, C6, $D$2:$D$709, D6, $E$2:$E$709, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="10"/>
@@ -22404,7 +22385,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B7, $C$2:$C$709, C7, $D$2:$D$709, D7, $E$2:$E$709, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="25"/>
@@ -22448,7 +22429,7 @@
         <v>3156</v>
       </c>
       <c r="N8" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B8, $C$2:$C$709, C8, $D$2:$D$709, D8, $E$2:$E$709, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="10"/>
@@ -22496,7 +22477,7 @@
         <v>350</v>
       </c>
       <c r="N9" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B9, $C$2:$C$709, C9, $D$2:$D$709, D9, $E$2:$E$709, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="10"/>
@@ -22535,7 +22516,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B10, $C$2:$C$709, C10, $D$2:$D$709, D10, $E$2:$E$709, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="19"/>
@@ -22576,7 +22557,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B11, $C$2:$C$709, C11, $D$2:$D$709, D11, $E$2:$E$709, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="29"/>
@@ -22623,7 +22604,7 @@
         <v>650</v>
       </c>
       <c r="N12" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B12, $C$2:$C$709, C12, $D$2:$D$709, D12, $E$2:$E$709, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="10"/>
@@ -22664,7 +22645,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B13, $C$2:$C$709, C13, $D$2:$D$709, D13, $E$2:$E$709, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="10"/>
@@ -22703,7 +22684,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B14, $C$2:$C$709, C14, $D$2:$D$709, D14, $E$2:$E$709, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14" s="10"/>
@@ -22751,7 +22732,7 @@
         <v>300</v>
       </c>
       <c r="N15" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B15, $C$2:$C$709, C15, $D$2:$D$709, D15, $E$2:$E$709, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O15" s="30"/>
@@ -22799,7 +22780,7 @@
         <v>200</v>
       </c>
       <c r="N16" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B16, $C$2:$C$709, C16, $D$2:$D$709, D16, $E$2:$E$709, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O16" s="30"/>
@@ -22840,7 +22821,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B17, $C$2:$C$709, C17, $D$2:$D$709, D17, $E$2:$E$709, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22886,7 +22867,7 @@
         <v>516</v>
       </c>
       <c r="N18" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B18, $C$2:$C$709, C18, $D$2:$D$709, D18, $E$2:$E$709, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18" s="10"/>
@@ -22934,7 +22915,7 @@
         <v>300</v>
       </c>
       <c r="N19" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B19, $C$2:$C$709, C19, $D$2:$D$709, D19, $E$2:$E$709, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P19" s="24"/>
@@ -22974,7 +22955,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B20, $C$2:$C$709, C20, $D$2:$D$709, D20, $E$2:$E$709, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23020,7 +23001,7 @@
         <v>500</v>
       </c>
       <c r="N21" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B21, $C$2:$C$709, C21, $D$2:$D$709, D21, $E$2:$E$709, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23057,7 +23038,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B22, $C$2:$C$709, C22, $D$2:$D$709, D22, $E$2:$E$709, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23103,7 +23084,7 @@
         <v>300</v>
       </c>
       <c r="N23" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B23, $C$2:$C$709, C23, $D$2:$D$709, D23, $E$2:$E$709, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23142,7 +23123,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B24, $C$2:$C$709, C24, $D$2:$D$709, D24, $E$2:$E$709, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24"/>
@@ -23190,7 +23171,7 @@
         <v>700</v>
       </c>
       <c r="N25" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B25, $C$2:$C$709, C25, $D$2:$D$709, D25, $E$2:$E$709, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23229,7 +23210,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B26, $C$2:$C$709, C26, $D$2:$D$709, D26, $E$2:$E$709, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26"/>
@@ -23277,7 +23258,7 @@
         <v>720</v>
       </c>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B27, $C$2:$C$709, C27, $D$2:$D$709, D27, $E$2:$E$709, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23316,7 +23297,7 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B28, $C$2:$C$709, C28, $D$2:$D$709, D28, $E$2:$E$709, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28"/>
@@ -23357,7 +23338,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B29, $C$2:$C$709, C29, $D$2:$D$709, D29, $E$2:$E$709, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29" s="10"/>
@@ -23406,7 +23387,7 @@
         <v>175</v>
       </c>
       <c r="N30" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B30, $C$2:$C$709, C30, $D$2:$D$709, D30, $E$2:$E$709, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23452,7 +23433,7 @@
         <v>650</v>
       </c>
       <c r="N31" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B31, $C$2:$C$709, C31, $D$2:$D$709, D31, $E$2:$E$709, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23489,7 +23470,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B32, $C$2:$C$709, C32, $D$2:$D$709, D32, $E$2:$E$709, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32"/>
@@ -23527,7 +23508,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B33, $C$2:$C$709, C33, $D$2:$D$709, D33, $E$2:$E$709, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33"/>
@@ -23567,7 +23548,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B34, $C$2:$C$709, C34, $D$2:$D$709, D34, $E$2:$E$709, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34"/>
@@ -23608,7 +23589,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B35, $C$2:$C$709, C35, $D$2:$D$709, D35, $E$2:$E$709, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P35"/>
@@ -23655,7 +23636,7 @@
         <v>300</v>
       </c>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B36, $C$2:$C$709, C36, $D$2:$D$709, D36, $E$2:$E$709, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23701,7 +23682,7 @@
         <v>525</v>
       </c>
       <c r="N37" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B37, $C$2:$C$709, C37, $D$2:$D$709, D37, $E$2:$E$709, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23748,7 +23729,7 @@
         <v>225</v>
       </c>
       <c r="N38" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B38, $C$2:$C$709, C38, $D$2:$D$709, D38, $E$2:$E$709, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23785,7 +23766,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B39, $C$2:$C$709, C39, $D$2:$D$709, D39, $E$2:$E$709, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39"/>
@@ -23824,7 +23805,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B40, $C$2:$C$709, C40, $D$2:$D$709, D40, $E$2:$E$709, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40"/>
@@ -23865,7 +23846,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B41, $C$2:$C$709, C41, $D$2:$D$709, D41, $E$2:$E$709, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41"/>
@@ -23906,7 +23887,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B42, $C$2:$C$709, C42, $D$2:$D$709, D42, $E$2:$E$709, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42"/>
@@ -23947,7 +23928,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B43, $C$2:$C$709, C43, $D$2:$D$709, D43, $E$2:$E$709, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43"/>
@@ -23985,7 +23966,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B44, $C$2:$C$709, C44, $D$2:$D$709, D44, $E$2:$E$709, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44"/>
@@ -24026,7 +24007,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B45, $C$2:$C$709, C45, $D$2:$D$709, D45, $E$2:$E$709, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -24067,7 +24048,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B46, $C$2:$C$709, C46, $D$2:$D$709, D46, $E$2:$E$709, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
@@ -24106,7 +24087,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B47, $C$2:$C$709, C47, $D$2:$D$709, D47, $E$2:$E$709, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -24154,7 +24135,7 @@
         <v>314</v>
       </c>
       <c r="N48" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B48, $C$2:$C$709, C48, $D$2:$D$709, D48, $E$2:$E$709, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24201,7 +24182,7 @@
         <v>540</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B49, $C$2:$C$709, C49, $D$2:$D$709, D49, $E$2:$E$709, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49"/>
@@ -24240,7 +24221,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B50, $C$2:$C$709, C50, $D$2:$D$709, D50, $E$2:$E$709, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50"/>
@@ -24281,7 +24262,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B51, $C$2:$C$709, C51, $D$2:$D$709, D51, $E$2:$E$709, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51"/>
@@ -24320,7 +24301,7 @@
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B52, $C$2:$C$709, C52, $D$2:$D$709, D52, $E$2:$E$709, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52"/>
@@ -24359,7 +24340,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B53, $C$2:$C$709, C53, $D$2:$D$709, D53, $E$2:$E$709, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53"/>
@@ -24400,7 +24381,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B54, $C$2:$C$709, C54, $D$2:$D$709, D54, $E$2:$E$709, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -24448,7 +24429,7 @@
         <v>300</v>
       </c>
       <c r="N55" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B55, $C$2:$C$709, C55, $D$2:$D$709, D55, $E$2:$E$709, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -24487,7 +24468,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B56, $C$2:$C$709, C56, $D$2:$D$709, D56, $E$2:$E$709, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56"/>
@@ -24526,7 +24507,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B57, $C$2:$C$709, C57, $D$2:$D$709, D57, $E$2:$E$709, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
@@ -24574,7 +24555,7 @@
         <v>250</v>
       </c>
       <c r="N58" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B58, $C$2:$C$709, C58, $D$2:$D$709, D58, $E$2:$E$709, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24611,7 +24592,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B59, $C$2:$C$709, C59, $D$2:$D$709, D59, $E$2:$E$709, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24648,7 +24629,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B60, $C$2:$C$709, C60, $D$2:$D$709, D60, $E$2:$E$709, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24694,7 +24675,7 @@
         <v>302</v>
       </c>
       <c r="N61" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B61, $C$2:$C$709, C61, $D$2:$D$709, D61, $E$2:$E$709, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61" s="10"/>
@@ -24737,7 +24718,7 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B62, $C$2:$C$709, C62, $D$2:$D$709, D62, $E$2:$E$709, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24774,7 +24755,7 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B63, $C$2:$C$709, C63, $D$2:$D$709, D63, $E$2:$E$709, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24813,7 +24794,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B64, $C$2:$C$709, C64, $D$2:$D$709, D64, $E$2:$E$709, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24850,7 +24831,7 @@
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B65, $C$2:$C$709, C65, $D$2:$D$709, D65, $E$2:$E$709, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65"/>
@@ -24889,7 +24870,7 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B66, $C$2:$C$709, C66, $D$2:$D$709, D66, $E$2:$E$709, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$709, B66, $C$2:$C$709, C66, $D$2:$D$709, D66, $E$2:$E$709, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66"/>
@@ -24928,7 +24909,7 @@
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B67, $C$2:$C$709, C67, $D$2:$D$709, D67, $E$2:$E$709, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67"/>
@@ -24969,7 +24950,7 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B68, $C$2:$C$709, C68, $D$2:$D$709, D68, $E$2:$E$709, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68"/>
@@ -25010,7 +24991,7 @@
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B69, $C$2:$C$709, C69, $D$2:$D$709, D69, $E$2:$E$709, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69"/>
@@ -25051,7 +25032,7 @@
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B70, $C$2:$C$709, C70, $D$2:$D$709, D70, $E$2:$E$709, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70"/>
@@ -25092,7 +25073,7 @@
       <c r="L71" s="17"/>
       <c r="M71" s="17"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B71, $C$2:$C$709, C71, $D$2:$D$709, D71, $E$2:$E$709, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O71"/>
@@ -25140,7 +25121,7 @@
         <v>10680</v>
       </c>
       <c r="N72" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B72, $C$2:$C$709, C72, $D$2:$D$709, D72, $E$2:$E$709, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25186,7 +25167,7 @@
         <v>1200</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B73, $C$2:$C$709, C73, $D$2:$D$709, D73, $E$2:$E$709, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25223,7 +25204,7 @@
       <c r="L74" s="17"/>
       <c r="M74" s="17"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B74, $C$2:$C$709, C74, $D$2:$D$709, D74, $E$2:$E$709, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74"/>
@@ -25264,7 +25245,7 @@
       <c r="L75" s="17"/>
       <c r="M75" s="17"/>
       <c r="N75" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B75, $C$2:$C$709, C75, $D$2:$D$709, D75, $E$2:$E$709, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O75"/>
@@ -25308,11 +25289,11 @@
         <v>17940</v>
       </c>
       <c r="M76" s="18">
-        <f t="shared" ref="M76:M83" si="0">ABS((D76*E76)-L76)</f>
+        <f t="shared" ref="M76:M83" si="2">ABS((D76*E76)-L76)</f>
         <v>10880</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B76, $C$2:$C$709, C76, $D$2:$D$709, D76, $E$2:$E$709, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25355,11 +25336,11 @@
         <v>8970</v>
       </c>
       <c r="M77" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B77, $C$2:$C$709, C77, $D$2:$D$709, D77, $E$2:$E$709, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25401,11 +25382,11 @@
         <v>8400</v>
       </c>
       <c r="M78" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N78" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B78, $C$2:$C$709, C78, $D$2:$D$709, D78, $E$2:$E$709, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78" s="10"/>
@@ -25449,11 +25430,11 @@
         <v>32900</v>
       </c>
       <c r="M79" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B79, $C$2:$C$709, C79, $D$2:$D$709, D79, $E$2:$E$709, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25495,11 +25476,11 @@
         <v>5585</v>
       </c>
       <c r="M80" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>395</v>
       </c>
       <c r="N80" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B80, $C$2:$C$709, C80, $D$2:$D$709, D80, $E$2:$E$709, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O80" s="39" t="s">
@@ -25545,11 +25526,11 @@
         <v>5730</v>
       </c>
       <c r="M81" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>250</v>
       </c>
       <c r="N81" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B81, $C$2:$C$709, C81, $D$2:$D$709, D81, $E$2:$E$709, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O81" s="39" t="s">
@@ -25595,11 +25576,11 @@
         <v>6367.2</v>
       </c>
       <c r="M82" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300.80000000000018</v>
       </c>
       <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B82, $C$2:$C$709, C82, $D$2:$D$709, D82, $E$2:$E$709, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25641,11 +25622,11 @@
         <v>11660</v>
       </c>
       <c r="M83" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B83, $C$2:$C$709, C83, $D$2:$D$709, D83, $E$2:$E$709, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O83" s="39" t="s">
@@ -25688,7 +25669,7 @@
       <c r="L84" s="17"/>
       <c r="M84" s="17"/>
       <c r="N84" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B84, $C$2:$C$709, C84, $D$2:$D$709, D84, $E$2:$E$709, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O84"/>
@@ -25736,7 +25717,7 @@
         <v>300</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B85, $C$2:$C$709, C85, $D$2:$D$709, D85, $E$2:$E$709, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25782,7 +25763,7 @@
         <v>295</v>
       </c>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B86, $C$2:$C$709, C86, $D$2:$D$709, D86, $E$2:$E$709, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25828,7 +25809,7 @@
         <v>250</v>
       </c>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B87, $C$2:$C$709, C87, $D$2:$D$709, D87, $E$2:$E$709, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25874,7 +25855,7 @@
         <v>200</v>
       </c>
       <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B88, $C$2:$C$709, C88, $D$2:$D$709, D88, $E$2:$E$709, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O88" s="39" t="s">
@@ -25911,7 +25892,7 @@
       </c>
       <c r="J89" s="35"/>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B89, $C$2:$C$709, C89, $D$2:$D$709, D89, $E$2:$E$709, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25953,11 +25934,11 @@
         <v>5755</v>
       </c>
       <c r="M90" s="28">
-        <f t="shared" ref="M90:M98" si="1">ABS((D90*E90)-L90)</f>
+        <f t="shared" ref="M90:M98" si="3">ABS((D90*E90)-L90)</f>
         <v>275</v>
       </c>
       <c r="N90" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B90, $C$2:$C$709, C90, $D$2:$D$709, D90, $E$2:$E$709, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O90" s="10"/>
@@ -26001,11 +25982,11 @@
         <v>5805</v>
       </c>
       <c r="M91" s="28">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+      <c r="N91" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>225</v>
-      </c>
-      <c r="N91" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B91, $C$2:$C$709, C91, $D$2:$D$709, D91, $E$2:$E$709, E91) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O91" s="10"/>
@@ -26049,11 +26030,11 @@
         <v>39300</v>
       </c>
       <c r="M92" s="18">
+        <f t="shared" si="3"/>
+        <v>18850</v>
+      </c>
+      <c r="N92" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>18850</v>
-      </c>
-      <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B92, $C$2:$C$709, C92, $D$2:$D$709, D92, $E$2:$E$709, E92) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26095,11 +26076,11 @@
         <v>19730.5</v>
       </c>
       <c r="M93" s="28">
+        <f t="shared" si="3"/>
+        <v>504.5</v>
+      </c>
+      <c r="N93" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>504.5</v>
-      </c>
-      <c r="N93" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B93, $C$2:$C$709, C93, $D$2:$D$709, D93, $E$2:$E$709, E93) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O93" s="39" t="s">
@@ -26145,11 +26126,11 @@
         <v>19690</v>
       </c>
       <c r="M94" s="28">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+      <c r="N94" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>545</v>
-      </c>
-      <c r="N94" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B94, $C$2:$C$709, C94, $D$2:$D$709, D94, $E$2:$E$709, E94) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O94" s="39" t="s">
@@ -26195,11 +26176,11 @@
         <v>10400</v>
       </c>
       <c r="M95" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N95" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B95, $C$2:$C$709, C95, $D$2:$D$709, D95, $E$2:$E$709, E95) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26241,11 +26222,11 @@
         <v>33200</v>
       </c>
       <c r="M96" s="18">
+        <f t="shared" si="3"/>
+        <v>1200</v>
+      </c>
+      <c r="N96" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>1200</v>
-      </c>
-      <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B96, $C$2:$C$709, C96, $D$2:$D$709, D96, $E$2:$E$709, E96) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26287,11 +26268,11 @@
         <v>4120</v>
       </c>
       <c r="M97" s="28">
+        <f t="shared" si="3"/>
+        <v>270</v>
+      </c>
+      <c r="N97" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>270</v>
-      </c>
-      <c r="N97" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B97, $C$2:$C$709, C97, $D$2:$D$709, D97, $E$2:$E$709, E97) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O97" s="29" t="s">
@@ -26337,11 +26318,11 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M98" s="28">
+        <f t="shared" si="3"/>
+        <v>188.60000000000014</v>
+      </c>
+      <c r="N98" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>188.60000000000014</v>
-      </c>
-      <c r="N98" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B98, $C$2:$C$709, C98, $D$2:$D$709, D98, $E$2:$E$709, E98) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O98" s="29" t="s">
@@ -26384,7 +26365,7 @@
       <c r="L99" s="17"/>
       <c r="M99" s="17"/>
       <c r="N99" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B99, $C$2:$C$709, C99, $D$2:$D$709, D99, $E$2:$E$709, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O99"/>
@@ -26432,7 +26413,7 @@
         <v>300</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B100, $C$2:$C$709, C100, $D$2:$D$709, D100, $E$2:$E$709, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26478,7 +26459,7 @@
         <v>646</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B101, $C$2:$C$709, C101, $D$2:$D$709, D101, $E$2:$E$709, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26524,7 +26505,7 @@
         <v>360</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B102, $C$2:$C$709, C102, $D$2:$D$709, D102, $E$2:$E$709, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="39" t="s">
@@ -26574,7 +26555,7 @@
         <v>450</v>
       </c>
       <c r="N103" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B103, $C$2:$C$709, C103, $D$2:$D$709, D103, $E$2:$E$709, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P103"/>
@@ -26611,7 +26592,7 @@
         <v>118</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B104, $C$2:$C$709, C104, $D$2:$D$709, D104, $E$2:$E$709, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26657,7 +26638,7 @@
         <v>850</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B105, $C$2:$C$709, C105, $D$2:$D$709, D105, $E$2:$E$709, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26703,7 +26684,7 @@
         <v>714</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B106, $C$2:$C$709, C106, $D$2:$D$709, D106, $E$2:$E$709, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26749,7 +26730,7 @@
         <v>300</v>
       </c>
       <c r="N107" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B107, $C$2:$C$709, C107, $D$2:$D$709, D107, $E$2:$E$709, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107"/>
@@ -26796,7 +26777,7 @@
         <v>300</v>
       </c>
       <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B108, $C$2:$C$709, C108, $D$2:$D$709, D108, $E$2:$E$709, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P108" s="19"/>
@@ -26843,7 +26824,7 @@
         <v>300</v>
       </c>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B109, $C$2:$C$709, C109, $D$2:$D$709, D109, $E$2:$E$709, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26877,7 +26858,7 @@
       </c>
       <c r="J110" s="35"/>
       <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B110, $C$2:$C$709, C110, $D$2:$D$709, D110, $E$2:$E$709, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26919,11 +26900,11 @@
         <v>8700</v>
       </c>
       <c r="M111" s="18">
-        <f t="shared" ref="M111:M120" si="2">ABS((D111*E111)-L111)</f>
+        <f t="shared" ref="M111:M120" si="4">ABS((D111*E111)-L111)</f>
         <v>300</v>
       </c>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B111, $C$2:$C$709, C111, $D$2:$D$709, D111, $E$2:$E$709, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26965,11 +26946,11 @@
         <v>4852</v>
       </c>
       <c r="M112" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B112, $C$2:$C$709, C112, $D$2:$D$709, D112, $E$2:$E$709, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27011,11 +26992,11 @@
         <v>5905</v>
       </c>
       <c r="M113" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>275</v>
       </c>
       <c r="N113" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B113, $C$2:$C$709, C113, $D$2:$D$709, D113, $E$2:$E$709, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27057,11 +27038,11 @@
         <v>10249</v>
       </c>
       <c r="M114" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4451</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B114, $C$2:$C$709, C114, $D$2:$D$709, D114, $E$2:$E$709, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O114" s="39" t="s">
@@ -27106,11 +27087,11 @@
         <v>39300</v>
       </c>
       <c r="M115" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>18350</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B115, $C$2:$C$709, C115, $D$2:$D$709, D115, $E$2:$E$709, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27152,11 +27133,11 @@
         <v>3400</v>
       </c>
       <c r="M116" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B116, $C$2:$C$709, C116, $D$2:$D$709, D116, $E$2:$E$709, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27198,11 +27179,11 @@
         <v>8480</v>
       </c>
       <c r="M117" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>280</v>
       </c>
       <c r="N117" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B117, $C$2:$C$709, C117, $D$2:$D$709, D117, $E$2:$E$709, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="39" t="s">
@@ -27247,11 +27228,11 @@
         <v>15075</v>
       </c>
       <c r="M118" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>645</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B118, $C$2:$C$709, C118, $D$2:$D$709, D118, $E$2:$E$709, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="39" t="s">
@@ -27296,11 +27277,11 @@
         <v>8420</v>
       </c>
       <c r="M119" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B119, $C$2:$C$709, C119, $D$2:$D$709, D119, $E$2:$E$709, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27342,11 +27323,11 @@
         <v>14440</v>
       </c>
       <c r="M120" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B120, $C$2:$C$709, C120, $D$2:$D$709, D120, $E$2:$E$709, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O120"/>
@@ -27389,7 +27370,7 @@
       <c r="L121" s="18"/>
       <c r="M121" s="18"/>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B121, $C$2:$C$709, C121, $D$2:$D$709, D121, $E$2:$E$709, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="10"/>
@@ -27437,7 +27418,7 @@
         <v>650</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B122, $C$2:$C$709, C122, $D$2:$D$709, D122, $E$2:$E$709, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="39" t="s">
@@ -27474,7 +27455,7 @@
       </c>
       <c r="J123" s="35"/>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B123, $C$2:$C$709, C123, $D$2:$D$709, D123, $E$2:$E$709, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O123" s="24"/>
@@ -27511,7 +27492,7 @@
         <v>118</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B124, $C$2:$C$709, C124, $D$2:$D$709, D124, $E$2:$E$709, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O124" s="39" t="s">
@@ -27561,7 +27542,7 @@
         <v>500</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B125, $C$2:$C$709, C125, $D$2:$D$709, D125, $E$2:$E$709, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27607,7 +27588,7 @@
         <v>500</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B126, $C$2:$C$709, C126, $D$2:$D$709, D126, $E$2:$E$709, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="40" t="s">
@@ -27646,7 +27627,7 @@
         <v>118</v>
       </c>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B127, $C$2:$C$709, C127, $D$2:$D$709, D127, $E$2:$E$709, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27692,7 +27673,7 @@
         <v>300</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B128, $C$2:$C$709, C128, $D$2:$D$709, D128, $E$2:$E$709, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27738,7 +27719,7 @@
         <v>150</v>
       </c>
       <c r="N129" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B129, $C$2:$C$709, C129, $D$2:$D$709, D129, $E$2:$E$709, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -27784,7 +27765,7 @@
         <v>250</v>
       </c>
       <c r="N130" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B130, $C$2:$C$709, C130, $D$2:$D$709, D130, $E$2:$E$709, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="5">IF(COUNTIFS( $B$2:$B$709, B130, $C$2:$C$709, C130, $D$2:$D$709, D130, $E$2:$E$709, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
     </row>
@@ -27818,7 +27799,7 @@
       </c>
       <c r="J131" s="35"/>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B131, $C$2:$C$709, C131, $D$2:$D$709, D131, $E$2:$E$709, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O131" s="39" t="s">
@@ -27864,11 +27845,11 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M132" s="18">
-        <f t="shared" ref="M132:M143" si="3">ABS((D132*E132)-L132)</f>
+        <f t="shared" ref="M132:M143" si="6">ABS((D132*E132)-L132)</f>
         <v>710.99999999999636</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B132, $C$2:$C$709, C132, $D$2:$D$709, D132, $E$2:$E$709, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P132"/>
@@ -27911,11 +27892,11 @@
         <v>16500</v>
       </c>
       <c r="M133" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1400</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B133, $C$2:$C$709, C133, $D$2:$D$709, D133, $E$2:$E$709, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O133" s="39" t="s">
@@ -27961,11 +27942,11 @@
         <v>10300</v>
       </c>
       <c r="M134" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B134, $C$2:$C$709, C134, $D$2:$D$709, D134, $E$2:$E$709, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P134" s="30"/>
@@ -28008,11 +27989,11 @@
         <v>10814</v>
       </c>
       <c r="M135" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>501</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B135, $C$2:$C$709, C135, $D$2:$D$709, D135, $E$2:$E$709, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O135" s="39" t="s">
@@ -28057,11 +28038,11 @@
         <v>5370</v>
       </c>
       <c r="M136" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>320</v>
       </c>
       <c r="N136" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B136, $C$2:$C$709, C136, $D$2:$D$709, D136, $E$2:$E$709, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O136" s="30"/>
@@ -28105,11 +28086,11 @@
         <v>2610</v>
       </c>
       <c r="M137" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>235</v>
       </c>
       <c r="N137" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B137, $C$2:$C$709, C137, $D$2:$D$709, D137, $E$2:$E$709, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="30"/>
@@ -28153,11 +28134,11 @@
         <v>73800</v>
       </c>
       <c r="M138" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>48320</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B138, $C$2:$C$709, C138, $D$2:$D$709, D138, $E$2:$E$709, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="39" t="s">
@@ -28203,11 +28184,11 @@
         <v>9470</v>
       </c>
       <c r="M139" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B139, $C$2:$C$709, C139, $D$2:$D$709, D139, $E$2:$E$709, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28249,11 +28230,11 @@
         <v>14200</v>
       </c>
       <c r="M140" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B140, $C$2:$C$709, C140, $D$2:$D$709, D140, $E$2:$E$709, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28295,11 +28276,11 @@
         <v>7578</v>
       </c>
       <c r="M141" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>294</v>
       </c>
       <c r="N141" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B141, $C$2:$C$709, C141, $D$2:$D$709, D141, $E$2:$E$709, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -28341,11 +28322,11 @@
         <v>7578</v>
       </c>
       <c r="M142" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>294</v>
       </c>
       <c r="N142" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B142, $C$2:$C$709, C142, $D$2:$D$709, D142, $E$2:$E$709, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -28387,11 +28368,11 @@
         <v>4968</v>
       </c>
       <c r="M143" s="58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>280</v>
       </c>
       <c r="N143" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B143, $C$2:$C$709, C143, $D$2:$D$709, D143, $E$2:$E$709, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28425,7 +28406,7 @@
       </c>
       <c r="J144" s="35"/>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B144, $C$2:$C$709, C144, $D$2:$D$709, D144, $E$2:$E$709, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O144" s="30"/>
@@ -28465,7 +28446,7 @@
         <v>144</v>
       </c>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B145, $C$2:$C$709, C145, $D$2:$D$709, D145, $E$2:$E$709, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28511,7 +28492,7 @@
         <v>1700</v>
       </c>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B146, $C$2:$C$709, C146, $D$2:$D$709, D146, $E$2:$E$709, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P146" s="10"/>
@@ -28548,7 +28529,7 @@
         <v>117</v>
       </c>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B147, $C$2:$C$709, C147, $D$2:$D$709, D147, $E$2:$E$709, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28590,11 +28571,11 @@
         <v>10410</v>
       </c>
       <c r="M148" s="18">
-        <f t="shared" ref="M148:M153" si="4">ABS((D148*E148)-L148)</f>
+        <f t="shared" ref="M148:M153" si="7">ABS((D148*E148)-L148)</f>
         <v>300</v>
       </c>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B148, $C$2:$C$709, C148, $D$2:$D$709, D148, $E$2:$E$709, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O148" s="30"/>
@@ -28637,11 +28618,11 @@
         <v>5520</v>
       </c>
       <c r="M149" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N149" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B149, $C$2:$C$709, C149, $D$2:$D$709, D149, $E$2:$E$709, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O149" s="39" t="s">
@@ -28686,11 +28667,11 @@
         <v>2657</v>
       </c>
       <c r="M150" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>253</v>
       </c>
       <c r="N150" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B150, $C$2:$C$709, C150, $D$2:$D$709, D150, $E$2:$E$709, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O150" s="39" t="s">
@@ -28735,11 +28716,11 @@
         <v>2554.5</v>
       </c>
       <c r="M151" s="28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>355.5</v>
       </c>
       <c r="N151" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B151, $C$2:$C$709, C151, $D$2:$D$709, D151, $E$2:$E$709, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O151" s="39" t="s">
@@ -28784,11 +28765,11 @@
         <v>4080</v>
       </c>
       <c r="M152" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B152, $C$2:$C$709, C152, $D$2:$D$709, D152, $E$2:$E$709, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O152" s="10"/>
@@ -28832,11 +28813,11 @@
         <v>18140</v>
       </c>
       <c r="M153" s="26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>650</v>
       </c>
       <c r="N153" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B153, $C$2:$C$709, C153, $D$2:$D$709, D153, $E$2:$E$709, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28872,7 +28853,7 @@
         <v>195</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B154, $C$2:$C$709, C154, $D$2:$D$709, D154, $E$2:$E$709, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28918,7 +28899,7 @@
         <v>300</v>
       </c>
       <c r="N155" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B155, $C$2:$C$709, C155, $D$2:$D$709, D155, $E$2:$E$709, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O155" s="30"/>
@@ -28966,7 +28947,7 @@
         <v>188</v>
       </c>
       <c r="N156" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B156, $C$2:$C$709, C156, $D$2:$D$709, D156, $E$2:$E$709, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O156" s="30"/>
@@ -29002,7 +28983,7 @@
       </c>
       <c r="J157" s="35"/>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B157, $C$2:$C$709, C157, $D$2:$D$709, D157, $E$2:$E$709, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29048,7 +29029,7 @@
         <v>500</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B158, $C$2:$C$709, C158, $D$2:$D$709, D158, $E$2:$E$709, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29094,7 +29075,7 @@
         <v>47900</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B159, $C$2:$C$709, C159, $D$2:$D$709, D159, $E$2:$E$709, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O159" s="39" t="s">
@@ -29131,7 +29112,7 @@
       </c>
       <c r="J160" s="35"/>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B160, $C$2:$C$709, C160, $D$2:$D$709, D160, $E$2:$E$709, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P160" s="30"/>
@@ -29174,11 +29155,11 @@
         <v>8049</v>
       </c>
       <c r="M161" s="18">
-        <f t="shared" ref="M161:M167" si="5">ABS((D161*E161)-L161)</f>
+        <f t="shared" ref="M161:M167" si="8">ABS((D161*E161)-L161)</f>
         <v>800</v>
       </c>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B161, $C$2:$C$709, C161, $D$2:$D$709, D161, $E$2:$E$709, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O161" s="39" t="s">
@@ -29223,11 +29204,11 @@
         <v>10510</v>
       </c>
       <c r="M162" s="18">
+        <f t="shared" si="8"/>
+        <v>300</v>
+      </c>
+      <c r="N162" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>300</v>
-      </c>
-      <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B162, $C$2:$C$709, C162, $D$2:$D$709, D162, $E$2:$E$709, E162) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O162" s="10"/>
@@ -29271,11 +29252,11 @@
         <v>25300</v>
       </c>
       <c r="M163" s="18">
+        <f t="shared" si="8"/>
+        <v>650</v>
+      </c>
+      <c r="N163" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>650</v>
-      </c>
-      <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B163, $C$2:$C$709, C163, $D$2:$D$709, D163, $E$2:$E$709, E163) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O163" s="39" t="s">
@@ -29321,11 +29302,11 @@
         <v>12480</v>
       </c>
       <c r="M164" s="18">
+        <f t="shared" si="8"/>
+        <v>495</v>
+      </c>
+      <c r="N164" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>495</v>
-      </c>
-      <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B164, $C$2:$C$709, C164, $D$2:$D$709, D164, $E$2:$E$709, E164) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O164" s="39" t="s">
@@ -29370,11 +29351,11 @@
         <v>8820</v>
       </c>
       <c r="M165" s="28">
+        <f t="shared" si="8"/>
+        <v>650</v>
+      </c>
+      <c r="N165" s="30" t="str">
         <f t="shared" si="5"/>
-        <v>650</v>
-      </c>
-      <c r="N165" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B165, $C$2:$C$709, C165, $D$2:$D$709, D165, $E$2:$E$709, E165) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O165" s="30"/>
@@ -29418,11 +29399,11 @@
         <v>36946</v>
       </c>
       <c r="M166" s="28">
+        <f t="shared" si="8"/>
+        <v>934</v>
+      </c>
+      <c r="N166" s="30" t="str">
         <f t="shared" si="5"/>
-        <v>934</v>
-      </c>
-      <c r="N166" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B166, $C$2:$C$709, C166, $D$2:$D$709, D166, $E$2:$E$709, E166) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O166" s="30"/>
@@ -29466,11 +29447,11 @@
         <v>14172.5</v>
       </c>
       <c r="M167" s="28">
+        <f t="shared" si="8"/>
+        <v>527.5</v>
+      </c>
+      <c r="N167" s="30" t="str">
         <f t="shared" si="5"/>
-        <v>527.5</v>
-      </c>
-      <c r="N167" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B167, $C$2:$C$709, C167, $D$2:$D$709, D167, $E$2:$E$709, E167) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O167" s="30"/>
@@ -29513,7 +29494,7 @@
       <c r="L168" s="28"/>
       <c r="M168" s="28"/>
       <c r="N168" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B168, $C$2:$C$709, C168, $D$2:$D$709, D168, $E$2:$E$709, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O168" s="30"/>
@@ -29551,7 +29532,7 @@
         <v>117</v>
       </c>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B169, $C$2:$C$709, C169, $D$2:$D$709, D169, $E$2:$E$709, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29587,7 +29568,7 @@
         <v>118</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B170, $C$2:$C$709, C170, $D$2:$D$709, D170, $E$2:$E$709, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29633,7 +29614,7 @@
         <v>140</v>
       </c>
       <c r="N171" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B171, $C$2:$C$709, C171, $D$2:$D$709, D171, $E$2:$E$709, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="P171" s="30"/>
@@ -29680,7 +29661,7 @@
         <v>300</v>
       </c>
       <c r="N172" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B172, $C$2:$C$709, C172, $D$2:$D$709, D172, $E$2:$E$709, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -29714,7 +29695,7 @@
       </c>
       <c r="J173" s="35"/>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B173, $C$2:$C$709, C173, $D$2:$D$709, D173, $E$2:$E$709, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29760,7 +29741,7 @@
         <v>300</v>
       </c>
       <c r="N174" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B174, $C$2:$C$709, C174, $D$2:$D$709, D174, $E$2:$E$709, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O174" s="39" t="s">
@@ -29800,7 +29781,7 @@
         <v>117</v>
       </c>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B175, $C$2:$C$709, C175, $D$2:$D$709, D175, $E$2:$E$709, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29846,7 +29827,7 @@
         <v>750</v>
       </c>
       <c r="N176" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B176, $C$2:$C$709, C176, $D$2:$D$709, D176, $E$2:$E$709, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O176" s="24"/>
@@ -29886,7 +29867,7 @@
         <v>118</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B177, $C$2:$C$709, C177, $D$2:$D$709, D177, $E$2:$E$709, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29932,7 +29913,7 @@
         <v>300</v>
       </c>
       <c r="N178" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B178, $C$2:$C$709, C178, $D$2:$D$709, D178, $E$2:$E$709, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29971,7 +29952,7 @@
       <c r="L179" s="18"/>
       <c r="M179" s="18"/>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B179, $C$2:$C$709, C179, $D$2:$D$709, D179, $E$2:$E$709, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O179" s="10"/>
@@ -30019,7 +30000,7 @@
         <v>650</v>
       </c>
       <c r="N180" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B180, $C$2:$C$709, C180, $D$2:$D$709, D180, $E$2:$E$709, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O180"/>
@@ -30067,7 +30048,7 @@
         <v>260</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B181, $C$2:$C$709, C181, $D$2:$D$709, D181, $E$2:$E$709, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30103,7 +30084,7 @@
         <v>118</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B182, $C$2:$C$709, C182, $D$2:$D$709, D182, $E$2:$E$709, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O182" s="39" t="s">
@@ -30152,7 +30133,7 @@
         <v>450</v>
       </c>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B183, $C$2:$C$709, C183, $D$2:$D$709, D183, $E$2:$E$709, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30198,7 +30179,7 @@
         <v>290</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B184, $C$2:$C$709, C184, $D$2:$D$709, D184, $E$2:$E$709, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30244,7 +30225,7 @@
         <v>880</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B185, $C$2:$C$709, C185, $D$2:$D$709, D185, $E$2:$E$709, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="39" t="s">
@@ -30293,7 +30274,7 @@
         <v>320</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B186, $C$2:$C$709, C186, $D$2:$D$709, D186, $E$2:$E$709, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30339,7 +30320,7 @@
         <v>448</v>
       </c>
       <c r="N187" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B187, $C$2:$C$709, C187, $D$2:$D$709, D187, $E$2:$E$709, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30373,7 +30354,7 @@
       </c>
       <c r="J188" s="35"/>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B188, $C$2:$C$709, C188, $D$2:$D$709, D188, $E$2:$E$709, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30412,7 +30393,7 @@
       <c r="L189" s="45"/>
       <c r="M189" s="45"/>
       <c r="N189" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B189, $C$2:$C$709, C189, $D$2:$D$709, D189, $E$2:$E$709, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O189" s="24"/>
@@ -30450,7 +30431,7 @@
       </c>
       <c r="J190" s="35"/>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B190, $C$2:$C$709, C190, $D$2:$D$709, D190, $E$2:$E$709, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30496,7 +30477,7 @@
         <v>250</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B191, $C$2:$C$709, C191, $D$2:$D$709, D191, $E$2:$E$709, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30542,7 +30523,7 @@
         <v>300</v>
       </c>
       <c r="N192" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B192, $C$2:$C$709, C192, $D$2:$D$709, D192, $E$2:$E$709, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30576,7 +30557,7 @@
       </c>
       <c r="J193" s="35"/>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B193, $C$2:$C$709, C193, $D$2:$D$709, D193, $E$2:$E$709, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30622,7 +30603,7 @@
         <v>47480</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B194, $C$2:$C$709, C194, $D$2:$D$709, D194, $E$2:$E$709, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="9">IF(COUNTIFS( $B$2:$B$709, B194, $C$2:$C$709, C194, $D$2:$D$709, D194, $E$2:$E$709, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -30668,7 +30649,7 @@
         <v>340</v>
       </c>
       <c r="N195" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B195, $C$2:$C$709, C195, $D$2:$D$709, D195, $E$2:$E$709, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30704,7 +30685,7 @@
         <v>118</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B196, $C$2:$C$709, C196, $D$2:$D$709, D196, $E$2:$E$709, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30750,7 +30731,7 @@
         <v>250</v>
       </c>
       <c r="N197" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B197, $C$2:$C$709, C197, $D$2:$D$709, D197, $E$2:$E$709, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30796,7 +30777,7 @@
         <v>1000</v>
       </c>
       <c r="N198" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B198, $C$2:$C$709, C198, $D$2:$D$709, D198, $E$2:$E$709, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O198" s="10"/>
@@ -30833,7 +30814,7 @@
         <v>55</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B199, $C$2:$C$709, C199, $D$2:$D$709, D199, $E$2:$E$709, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30879,7 +30860,7 @@
         <v>250</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B200, $C$2:$C$709, C200, $D$2:$D$709, D200, $E$2:$E$709, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P200" s="30"/>
@@ -30916,7 +30897,7 @@
         <v>117</v>
       </c>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B201, $C$2:$C$709, C201, $D$2:$D$709, D201, $E$2:$E$709, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30950,7 +30931,7 @@
       </c>
       <c r="J202" s="35"/>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B202, $C$2:$C$709, C202, $D$2:$D$709, D202, $E$2:$E$709, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30996,7 +30977,7 @@
         <v>300</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B203, $C$2:$C$709, C203, $D$2:$D$709, D203, $E$2:$E$709, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31042,7 +31023,7 @@
         <v>300</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B204, $C$2:$C$709, C204, $D$2:$D$709, D204, $E$2:$E$709, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P204" s="25"/>
@@ -31089,7 +31070,7 @@
         <v>810</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B205, $C$2:$C$709, C205, $D$2:$D$709, D205, $E$2:$E$709, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31135,7 +31116,7 @@
         <v>646</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B206, $C$2:$C$709, C206, $D$2:$D$709, D206, $E$2:$E$709, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="39" t="s">
@@ -31177,7 +31158,7 @@
       <c r="L207" s="18"/>
       <c r="M207" s="18"/>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B207, $C$2:$C$709, C207, $D$2:$D$709, D207, $E$2:$E$709, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O207" s="10"/>
@@ -31225,7 +31206,7 @@
         <v>360</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B208, $C$2:$C$709, C208, $D$2:$D$709, D208, $E$2:$E$709, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31271,7 +31252,7 @@
         <v>300</v>
       </c>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B209, $C$2:$C$709, C209, $D$2:$D$709, D209, $E$2:$E$709, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31317,7 +31298,7 @@
         <v>816</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B210, $C$2:$C$709, C210, $D$2:$D$709, D210, $E$2:$E$709, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31353,7 +31334,7 @@
         <v>55</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B211, $C$2:$C$709, C211, $D$2:$D$709, D211, $E$2:$E$709, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31389,7 +31370,7 @@
         <v>117</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B212, $C$2:$C$709, C212, $D$2:$D$709, D212, $E$2:$E$709, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31423,7 +31404,7 @@
       </c>
       <c r="J213" s="35"/>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B213, $C$2:$C$709, C213, $D$2:$D$709, D213, $E$2:$E$709, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31459,7 +31440,7 @@
         <v>118</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B214, $C$2:$C$709, C214, $D$2:$D$709, D214, $E$2:$E$709, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O214" s="30"/>
@@ -31496,7 +31477,7 @@
         <v>118</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B215, $C$2:$C$709, C215, $D$2:$D$709, D215, $E$2:$E$709, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O215" s="30"/>
@@ -31538,7 +31519,7 @@
       <c r="L216" s="17"/>
       <c r="M216" s="17"/>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B216, $C$2:$C$709, C216, $D$2:$D$709, D216, $E$2:$E$709, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31584,7 +31565,7 @@
         <v>940</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B217, $C$2:$C$709, C217, $D$2:$D$709, D217, $E$2:$E$709, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31620,7 +31601,7 @@
         <v>118</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B218, $C$2:$C$709, C218, $D$2:$D$709, D218, $E$2:$E$709, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31659,7 +31640,7 @@
         <v>146</v>
       </c>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B219, $C$2:$C$709, C219, $D$2:$D$709, D219, $E$2:$E$709, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31695,7 +31676,7 @@
         <v>117</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B220, $C$2:$C$709, C220, $D$2:$D$709, D220, $E$2:$E$709, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P220" s="30"/>
@@ -31742,7 +31723,7 @@
         <v>300</v>
       </c>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B221, $C$2:$C$709, C221, $D$2:$D$709, D221, $E$2:$E$709, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="39" t="s">
@@ -31792,7 +31773,7 @@
         <v>651</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B222, $C$2:$C$709, C222, $D$2:$D$709, D222, $E$2:$E$709, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31828,7 +31809,7 @@
         <v>117</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B223, $C$2:$C$709, C223, $D$2:$D$709, D223, $E$2:$E$709, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31864,7 +31845,7 @@
         <v>117</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B224, $C$2:$C$709, C224, $D$2:$D$709, D224, $E$2:$E$709, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31910,7 +31891,7 @@
         <v>650</v>
       </c>
       <c r="N225" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B225, $C$2:$C$709, C225, $D$2:$D$709, D225, $E$2:$E$709, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P225" s="30"/>
@@ -31957,7 +31938,7 @@
         <v>450</v>
       </c>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B226, $C$2:$C$709, C226, $D$2:$D$709, D226, $E$2:$E$709, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31991,7 +31972,7 @@
       </c>
       <c r="J227" s="35"/>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B227, $C$2:$C$709, C227, $D$2:$D$709, D227, $E$2:$E$709, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32027,7 +32008,7 @@
         <v>154</v>
       </c>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B228, $C$2:$C$709, C228, $D$2:$D$709, D228, $E$2:$E$709, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32073,7 +32054,7 @@
         <v>1800</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B229, $C$2:$C$709, C229, $D$2:$D$709, D229, $E$2:$E$709, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32109,7 +32090,7 @@
         <v>118</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B230, $C$2:$C$709, C230, $D$2:$D$709, D230, $E$2:$E$709, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32143,7 +32124,7 @@
       </c>
       <c r="J231" s="35"/>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B231, $C$2:$C$709, C231, $D$2:$D$709, D231, $E$2:$E$709, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32177,7 +32158,7 @@
       </c>
       <c r="J232" s="35"/>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B232, $C$2:$C$709, C232, $D$2:$D$709, D232, $E$2:$E$709, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32223,7 +32204,7 @@
         <v>400</v>
       </c>
       <c r="N233" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B233, $C$2:$C$709, C233, $D$2:$D$709, D233, $E$2:$E$709, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32259,7 +32240,7 @@
         <v>117</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B234, $C$2:$C$709, C234, $D$2:$D$709, D234, $E$2:$E$709, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32293,7 +32274,7 @@
       </c>
       <c r="J235" s="35"/>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B235, $C$2:$C$709, C235, $D$2:$D$709, D235, $E$2:$E$709, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32329,7 +32310,7 @@
         <v>117</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B236, $C$2:$C$709, C236, $D$2:$D$709, D236, $E$2:$E$709, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32375,7 +32356,7 @@
         <v>500</v>
       </c>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B237, $C$2:$C$709, C237, $D$2:$D$709, D237, $E$2:$E$709, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O237" s="39" t="s">
@@ -32412,7 +32393,7 @@
       </c>
       <c r="J238" s="35"/>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B238, $C$2:$C$709, C238, $D$2:$D$709, D238, $E$2:$E$709, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32458,7 +32439,7 @@
         <v>650</v>
       </c>
       <c r="N239" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B239, $C$2:$C$709, C239, $D$2:$D$709, D239, $E$2:$E$709, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P239" s="30"/>
@@ -32505,7 +32486,7 @@
         <v>300</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B240, $C$2:$C$709, C240, $D$2:$D$709, D240, $E$2:$E$709, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32539,7 +32520,7 @@
       </c>
       <c r="J241" s="35"/>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B241, $C$2:$C$709, C241, $D$2:$D$709, D241, $E$2:$E$709, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32575,7 +32556,7 @@
         <v>118</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B242, $C$2:$C$709, C242, $D$2:$D$709, D242, $E$2:$E$709, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32621,7 +32602,7 @@
         <v>800</v>
       </c>
       <c r="N243" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B243, $C$2:$C$709, C243, $D$2:$D$709, D243, $E$2:$E$709, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32667,7 +32648,7 @@
         <v>268</v>
       </c>
       <c r="N244" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B244, $C$2:$C$709, C244, $D$2:$D$709, D244, $E$2:$E$709, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32706,7 +32687,7 @@
       <c r="L245" s="18"/>
       <c r="M245" s="18"/>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B245, $C$2:$C$709, C245, $D$2:$D$709, D245, $E$2:$E$709, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="10"/>
@@ -32747,7 +32728,7 @@
       <c r="L246" s="18"/>
       <c r="M246" s="18"/>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B246, $C$2:$C$709, C246, $D$2:$D$709, D246, $E$2:$E$709, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O246" s="10"/>
@@ -32795,7 +32776,7 @@
         <v>370</v>
       </c>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B247, $C$2:$C$709, C247, $D$2:$D$709, D247, $E$2:$E$709, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P247" s="30"/>
@@ -32830,7 +32811,7 @@
       </c>
       <c r="J248" s="35"/>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B248, $C$2:$C$709, C248, $D$2:$D$709, D248, $E$2:$E$709, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32866,7 +32847,7 @@
         <v>118</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B249, $C$2:$C$709, C249, $D$2:$D$709, D249, $E$2:$E$709, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O249" s="30"/>
@@ -32913,7 +32894,7 @@
         <v>650</v>
       </c>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B250, $C$2:$C$709, C250, $D$2:$D$709, D250, $E$2:$E$709, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O250" s="30"/>
@@ -32950,7 +32931,7 @@
         <v>118</v>
       </c>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B251, $C$2:$C$709, C251, $D$2:$D$709, D251, $E$2:$E$709, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32986,7 +32967,7 @@
         <v>118</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B252, $C$2:$C$709, C252, $D$2:$D$709, D252, $E$2:$E$709, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33020,7 +33001,7 @@
       </c>
       <c r="J253" s="35"/>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B253, $C$2:$C$709, C253, $D$2:$D$709, D253, $E$2:$E$709, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33066,7 +33047,7 @@
         <v>285</v>
       </c>
       <c r="N254" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B254, $C$2:$C$709, C254, $D$2:$D$709, D254, $E$2:$E$709, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33112,7 +33093,7 @@
         <v>726</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B255, $C$2:$C$709, C255, $D$2:$D$709, D255, $E$2:$E$709, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33146,7 +33127,7 @@
       </c>
       <c r="J256" s="35"/>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B256, $C$2:$C$709, C256, $D$2:$D$709, D256, $E$2:$E$709, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33180,7 +33161,7 @@
       </c>
       <c r="J257" s="35"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B257, $C$2:$C$709, C257, $D$2:$D$709, D257, $E$2:$E$709, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33226,7 +33207,7 @@
         <v>300</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B258, $C$2:$C$709, C258, $D$2:$D$709, D258, $E$2:$E$709, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N295" si="10">IF(COUNTIFS( $B$2:$B$709, B258, $C$2:$C$709, C258, $D$2:$D$709, D258, $E$2:$E$709, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O258" s="10"/>
@@ -33274,7 +33255,7 @@
         <v>250</v>
       </c>
       <c r="N259" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B259, $C$2:$C$709, C259, $D$2:$D$709, D259, $E$2:$E$709, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33308,7 +33289,7 @@
       </c>
       <c r="J260" s="35"/>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B260, $C$2:$C$709, C260, $D$2:$D$709, D260, $E$2:$E$709, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="30"/>
@@ -33343,7 +33324,7 @@
       </c>
       <c r="J261" s="35"/>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B261, $C$2:$C$709, C261, $D$2:$D$709, D261, $E$2:$E$709, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33389,7 +33370,7 @@
         <v>260</v>
       </c>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B262, $C$2:$C$709, C262, $D$2:$D$709, D262, $E$2:$E$709, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O262" s="10"/>
@@ -33427,7 +33408,7 @@
         <v>117</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B263, $C$2:$C$709, C263, $D$2:$D$709, D263, $E$2:$E$709, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33473,7 +33454,7 @@
         <v>300</v>
       </c>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B264, $C$2:$C$709, C264, $D$2:$D$709, D264, $E$2:$E$709, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33507,7 +33488,7 @@
       </c>
       <c r="J265" s="35"/>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B265, $C$2:$C$709, C265, $D$2:$D$709, D265, $E$2:$E$709, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33541,7 +33522,7 @@
       </c>
       <c r="J266" s="35"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B266, $C$2:$C$709, C266, $D$2:$D$709, D266, $E$2:$E$709, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33578,7 +33559,7 @@
       <c r="L267" s="18"/>
       <c r="M267" s="18"/>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B267, $C$2:$C$709, C267, $D$2:$D$709, D267, $E$2:$E$709, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P267" s="10"/>
@@ -33616,7 +33597,7 @@
       <c r="L268" s="18"/>
       <c r="M268" s="18"/>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B268, $C$2:$C$709, C268, $D$2:$D$709, D268, $E$2:$E$709, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O268" s="10"/>
@@ -33664,7 +33645,7 @@
         <v>250</v>
       </c>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B269, $C$2:$C$709, C269, $D$2:$D$709, D269, $E$2:$E$709, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33710,7 +33691,7 @@
         <v>275</v>
       </c>
       <c r="N270" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B270, $C$2:$C$709, C270, $D$2:$D$709, D270, $E$2:$E$709, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33747,7 +33728,7 @@
       <c r="L271" s="18"/>
       <c r="M271" s="18"/>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B271, $C$2:$C$709, C271, $D$2:$D$709, D271, $E$2:$E$709, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O271" s="10"/>
@@ -33795,7 +33776,7 @@
         <v>250</v>
       </c>
       <c r="N272" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B272, $C$2:$C$709, C272, $D$2:$D$709, D272, $E$2:$E$709, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P272" s="30"/>
@@ -33842,7 +33823,7 @@
         <v>300</v>
       </c>
       <c r="N273" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B273, $C$2:$C$709, C273, $D$2:$D$709, D273, $E$2:$E$709, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33881,7 +33862,7 @@
       <c r="L274" s="18"/>
       <c r="M274" s="18"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B274, $C$2:$C$709, C274, $D$2:$D$709, D274, $E$2:$E$709, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O274" s="10"/>
@@ -33920,7 +33901,7 @@
       <c r="L275" s="18"/>
       <c r="M275" s="18"/>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B275, $C$2:$C$709, C275, $D$2:$D$709, D275, $E$2:$E$709, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O275" s="10"/>
@@ -33967,7 +33948,7 @@
         <v>480</v>
       </c>
       <c r="N276" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B276, $C$2:$C$709, C276, $D$2:$D$709, D276, $E$2:$E$709, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34003,7 +33984,7 @@
         <v>118</v>
       </c>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B277, $C$2:$C$709, C277, $D$2:$D$709, D277, $E$2:$E$709, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34037,7 +34018,7 @@
       </c>
       <c r="J278" s="35"/>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B278, $C$2:$C$709, C278, $D$2:$D$709, D278, $E$2:$E$709, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34073,7 +34054,7 @@
         <v>118</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B279, $C$2:$C$709, C279, $D$2:$D$709, D279, $E$2:$E$709, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34107,7 +34088,7 @@
       </c>
       <c r="J280" s="35"/>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B280, $C$2:$C$709, C280, $D$2:$D$709, D280, $E$2:$E$709, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P280" s="30"/>
@@ -34144,7 +34125,7 @@
         <v>118</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B281, $C$2:$C$709, C281, $D$2:$D$709, D281, $E$2:$E$709, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34178,7 +34159,7 @@
       </c>
       <c r="J282" s="35"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B282, $C$2:$C$709, C282, $D$2:$D$709, D282, $E$2:$E$709, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34224,7 +34205,7 @@
         <v>250</v>
       </c>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B283, $C$2:$C$709, C283, $D$2:$D$709, D283, $E$2:$E$709, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34270,7 +34251,7 @@
         <v>300</v>
       </c>
       <c r="N284" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B284, $C$2:$C$709, C284, $D$2:$D$709, D284, $E$2:$E$709, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34304,7 +34285,7 @@
       </c>
       <c r="J285" s="35"/>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B285, $C$2:$C$709, C285, $D$2:$D$709, D285, $E$2:$E$709, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34340,7 +34321,7 @@
         <v>118</v>
       </c>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B286, $C$2:$C$709, C286, $D$2:$D$709, D286, $E$2:$E$709, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34376,7 +34357,7 @@
         <v>55</v>
       </c>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B287, $C$2:$C$709, C287, $D$2:$D$709, D287, $E$2:$E$709, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34410,7 +34391,7 @@
       </c>
       <c r="J288" s="35"/>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B288, $C$2:$C$709, C288, $D$2:$D$709, D288, $E$2:$E$709, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34444,7 +34425,7 @@
       </c>
       <c r="J289" s="35"/>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B289, $C$2:$C$709, C289, $D$2:$D$709, D289, $E$2:$E$709, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34483,7 +34464,7 @@
       <c r="L290" s="28"/>
       <c r="M290" s="28"/>
       <c r="N290" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B290, $C$2:$C$709, C290, $D$2:$D$709, D290, $E$2:$E$709, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O290" s="30"/>
@@ -34524,7 +34505,7 @@
       <c r="L291" s="28"/>
       <c r="M291" s="28"/>
       <c r="N291" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B291, $C$2:$C$709, C291, $D$2:$D$709, D291, $E$2:$E$709, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34563,7 +34544,7 @@
       <c r="L292" s="18"/>
       <c r="M292" s="18"/>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B292, $C$2:$C$709, C292, $D$2:$D$709, D292, $E$2:$E$709, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O292" s="10"/>
@@ -34603,7 +34584,7 @@
         <v>654</v>
       </c>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B293, $C$2:$C$709, C293, $D$2:$D$709, D293, $E$2:$E$709, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34637,11 +34618,11 @@
         <v>10250</v>
       </c>
       <c r="M294" s="18">
-        <f t="shared" ref="M294:M295" si="6">ABS((D294*E294)-L294)</f>
+        <f t="shared" ref="M294:M295" si="11">ABS((D294*E294)-L294)</f>
         <v>300</v>
       </c>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B294, $C$2:$C$709, C294, $D$2:$D$709, D294, $E$2:$E$709, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34675,11 +34656,11 @@
         <v>3245</v>
       </c>
       <c r="M295" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>240</v>
       </c>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$709, B295, $C$2:$C$709, C295, $D$2:$D$709, D295, $E$2:$E$709, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
